--- a/testdata/passedtestcases/jpmorgan_drake_import.xlsx
+++ b/testdata/passedtestcases/jpmorgan_drake_import.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1569" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1569" uniqueCount="343">
   <si>
     <t>TSJ</t>
   </si>
@@ -64,280 +64,439 @@
     <t>CALL NBIS NEBIUS GROUP N V</t>
   </si>
   <si>
-    <t>CALL NVTS</t>
+    <t>CALL NVTS NEBIUS GROUP N V NAVITAS SEMICONDUCTOR CRPRTN</t>
   </si>
   <si>
     <t>NAVITAS SEMICONDUCTOR CRPRTN</t>
   </si>
   <si>
-    <t>CALL CRWV COREWEAVE INC CLASS A</t>
-  </si>
-  <si>
-    <t>PUT MSFT MICROSOFT CORP</t>
-  </si>
-  <si>
-    <t>CALL NBIS</t>
+    <t>CALL CRWV NAVITAS SEMICONDUCTOR CRPRTN COREWEAVE INC CLASS A</t>
+  </si>
+  <si>
+    <t>PUT MSFT COREWEAVE INC CLASS A MICROSOFT CORP</t>
+  </si>
+  <si>
+    <t>CALL NBIS MICROSOFT CORP NEBIUS GROUP N V</t>
   </si>
   <si>
     <t>NEBIUS GROUP N V</t>
   </si>
   <si>
-    <t>PUT NVDA NVIDIA CORPORATION</t>
-  </si>
-  <si>
-    <t>PUT RGTI</t>
+    <t>CALL NBIS NEBIUS GROUP N V NEBIUS GROUP N V</t>
+  </si>
+  <si>
+    <t>PUT NVDA NEBIUS GROUP N V NVIDIA CORPORATION</t>
+  </si>
+  <si>
+    <t>PUT RGTI NVIDIA CORPORATION RIGETTI COMPUTING INC</t>
   </si>
   <si>
     <t>RIGETTI COMPUTING INC</t>
   </si>
   <si>
-    <t>PUT QBTS D WAVE QUANTUM INC</t>
-  </si>
-  <si>
-    <t>PUT FVRR FIVERR INTERNATIONAL LTD</t>
-  </si>
-  <si>
-    <t>CALL GLXY GALAXY DIGITAL INC CL A</t>
-  </si>
-  <si>
-    <t>CALL GLXY</t>
+    <t>PUT QBTS RIGETTI COMPUTING INC D WAVE QUANTUM INC</t>
+  </si>
+  <si>
+    <t>PUT QBTS D WAVE QUANTUM INC D WAVE QUANTUM INC</t>
+  </si>
+  <si>
+    <t>PUT FVRR D WAVE QUANTUM INC FIVERR INTERNATIONAL LTD</t>
+  </si>
+  <si>
+    <t>PUT FVRR FIVERR INTERNATIONAL LTD FIVERR INTERNATIONAL LTD</t>
+  </si>
+  <si>
+    <t>CALL GLXY FIVERR INTERNATIONAL LTD GALAXY DIGITAL INC CL A</t>
+  </si>
+  <si>
+    <t>CALL GLXY GALAXY DIGITAL INC CL A GALAXY DIGITAL INC CL A</t>
+  </si>
+  <si>
+    <t>CALL NBIS GALAXY DIGITAL INC CL A NEBIUS GROUP N V</t>
+  </si>
+  <si>
+    <t>CALL GLXY NEBIUS GROUP N V GALAXY DIGITAL INC CL A</t>
   </si>
   <si>
     <t>GALAXY DIGITAL INC CL A</t>
   </si>
   <si>
-    <t>PUT CRWV</t>
+    <t>PUT CRWV NEBIUS GROUP N V COREWEAVE INC CLASS A</t>
   </si>
   <si>
     <t>COREWEAVE INC CLASS A</t>
   </si>
   <si>
-    <t>PUT NBIS</t>
-  </si>
-  <si>
-    <t>PUT NFLX NETFLIX INC</t>
-  </si>
-  <si>
-    <t>CALL NFLX NETFLIX INC ADJ 10:1 STOCK SPLIT</t>
-  </si>
-  <si>
-    <t>PUT NFLX</t>
+    <t>PUT NBIS COREWEAVE INC CLASS A NEBIUS GROUP N V</t>
+  </si>
+  <si>
+    <t>PUT NFLX GALAXY DIGITAL INC CL A NETFLIX INC</t>
+  </si>
+  <si>
+    <t>CALL NFLX NETFLIX INC NETFLIX INC ADJ 10:1 STOCK SPLIT</t>
+  </si>
+  <si>
+    <t>PUT NFLX ADJ 10:1 STOCK SPLIT NETFLIX INC</t>
   </si>
   <si>
     <t>NETFLIX INC</t>
   </si>
   <si>
-    <t>PUT NFLX NETFLIX INC ADJ 10:1 STOCK SPLIT</t>
-  </si>
-  <si>
-    <t>CALL NFLX</t>
+    <t>PUT NFLX NETFLIX INC NETFLIX INC ADJ 10:1 STOCK SPLIT</t>
+  </si>
+  <si>
+    <t>CALL NFLX ADJ 10:1 STOCK SPLIT NETFLIX INC</t>
   </si>
   <si>
     <t>ADJ 10:1 STOCK SPLIT</t>
   </si>
   <si>
-    <t>CALL RZLV</t>
+    <t>CALL NFLX NETFLIX INC NETFLIX INC</t>
+  </si>
+  <si>
+    <t>CALL RZLV NETFLIX INC REZOLVE AI PLC</t>
   </si>
   <si>
     <t>REZOLVE AI PLC</t>
   </si>
   <si>
-    <t>PUT NVDA</t>
+    <t>PUT NVDA REZOLVE AI PLC</t>
+  </si>
+  <si>
+    <t>PUT PLTR REZOLVE AI PLC PALANTIR TECHNOLOGIES INC CL</t>
   </si>
   <si>
     <t>PUT PLTR PALANTIR TECHNOLOGIES INC CL</t>
   </si>
   <si>
-    <t>PUT PLTR</t>
-  </si>
-  <si>
-    <t>PUT TSLA</t>
+    <t>PALANTIR TECHNOLOGIES INC CL</t>
+  </si>
+  <si>
+    <t>PUT RGTI PALANTIR TECHNOLOGIES INC CL</t>
+  </si>
+  <si>
+    <t>PUT TSLA PALANTIR TECHNOLOGIES INC CL TESLA INC</t>
   </si>
   <si>
     <t>TESLA INC</t>
   </si>
   <si>
+    <t>CALL OPEN TESLA INC OPENDOOR TECHNOLOGIES INC</t>
+  </si>
+  <si>
+    <t>CALL OPEN OPENDOOR TECHNOLOGIES INC OPENDOOR TECHNOLOGIES INC</t>
+  </si>
+  <si>
+    <t>OPENDOOR TECHNOLOGIES INC</t>
+  </si>
+  <si>
+    <t>CALL AMD OPENDOOR TECHNOLOGIES INC ADVANCED MICRO DEVICES INC</t>
+  </si>
+  <si>
+    <t>PUT AMD ADVANCED MICRO DEVICES INC ADVANCED MICRO DEVICES INC</t>
+  </si>
+  <si>
+    <t>ADVANCED MICRO DEVICES INC</t>
+  </si>
+  <si>
+    <t>CALL CRWV ADVANCED MICRO DEVICES INC COREWEAVE INC CLASS A</t>
+  </si>
+  <si>
+    <t>CALL NFLX COREWEAVE INC CLASS A NETFLIX INC</t>
+  </si>
+  <si>
+    <t>CALL GLXY NETFLIX INC GALAXY DIGITAL INC CL A</t>
+  </si>
+  <si>
+    <t>PUT NVDA GALAXY DIGITAL INC CL A NVIDIA CORPORATION</t>
+  </si>
+  <si>
+    <t>PUT PLTR NVIDIA CORPORATION PALANTIR TECHNOLOGIES INC CL</t>
+  </si>
+  <si>
+    <t>PUT PLTR PALANTIR TECHNOLOGIES INC CL PALANTIR TECHNOLOGIES INC CL ADJ 1:4 REV SPLIT D:25 SITC</t>
+  </si>
+  <si>
+    <t>CALL RZLV ADJ 1:4 REV SPLIT D:25 SITC REZOLVE AI PLC</t>
+  </si>
+  <si>
+    <t>PUT META REZOLVE AI PLC META PLATFORMS INC CL A</t>
+  </si>
+  <si>
+    <t>PUT MSFT META PLATFORMS INC CL A MICROSOFT CORP</t>
+  </si>
+  <si>
+    <t>MICROSOFT CORP</t>
+  </si>
+  <si>
+    <t>PUT AMD MICROSOFT CORP</t>
+  </si>
+  <si>
+    <t>CALL GOOG MICROSOFT CORP ALPHABET INC CLASS C</t>
+  </si>
+  <si>
+    <t>CALL OPEN ALPHABET INC CLASS C OPENDOOR TECHNOLOGIES INC</t>
+  </si>
+  <si>
+    <t>PUT SPY OPENDOOR TECHNOLOGIES INC</t>
+  </si>
+  <si>
+    <t>PUT CRWV OPENDOOR TECHNOLOGIES INC COREWEAVE INC CLASS A</t>
+  </si>
+  <si>
+    <t>CALL OPEN COREWEAVE INC CLASS A</t>
+  </si>
+  <si>
+    <t>CALL OPEN COREWEAVE INC CLASS A OPENDOOR TECHNOLOGIES INC</t>
+  </si>
+  <si>
     <t>CALL OPEN OPENDOOR TECHNOLOGIES INC</t>
   </si>
   <si>
-    <t>CALL OPEN</t>
-  </si>
-  <si>
-    <t>OPENDOOR TECHNOLOGIES INC</t>
-  </si>
-  <si>
-    <t>CALL AMD ADVANCED MICRO DEVICES INC</t>
-  </si>
-  <si>
-    <t>PUT AMD</t>
-  </si>
-  <si>
-    <t>ADVANCED MICRO DEVICES INC</t>
-  </si>
-  <si>
-    <t>PALANTIR TECHNOLOGIES INC CL</t>
-  </si>
-  <si>
-    <t>PUT PLTR PALANTIR TECHNOLOGIES INC CL ADJ 1:4 REV SPLIT D:25 SITC</t>
-  </si>
-  <si>
-    <t>PUT META META PLATFORMS INC CL A</t>
-  </si>
-  <si>
-    <t>PUT MSFT</t>
-  </si>
-  <si>
-    <t>MICROSOFT CORP</t>
-  </si>
-  <si>
-    <t>CALL GOOG ALPHABET INC CLASS C</t>
-  </si>
-  <si>
-    <t>PUT SPY</t>
-  </si>
-  <si>
-    <t>PUT CRWV COREWEAVE INC CLASS A</t>
-  </si>
-  <si>
-    <t>PUT OPEN OPENDOOR TECHNOLOGIES INC</t>
-  </si>
-  <si>
-    <t>CALL POET POET TECHNOLOGIES INC</t>
-  </si>
-  <si>
-    <t>RGTI</t>
-  </si>
-  <si>
-    <t>CALL AVGO BROADCOM INC</t>
-  </si>
-  <si>
-    <t>CALL APLD</t>
+    <t>PUT OPEN OPENDOOR TECHNOLOGIES INC OPENDOOR TECHNOLOGIES INC</t>
+  </si>
+  <si>
+    <t>CALL POET OPENDOOR TECHNOLOGIES INC POET TECHNOLOGIES INC RGTI 45954 42</t>
+  </si>
+  <si>
+    <t>RGTI 45954 42</t>
+  </si>
+  <si>
+    <t>CALL AVGO RIGETTI COMPUTING INC BROADCOM INC</t>
+  </si>
+  <si>
+    <t>CALL APLD BROADCOM INC APPLIED DIGITAL CORPORATION</t>
   </si>
   <si>
     <t>APPLIED DIGITAL CORPORATION</t>
   </si>
   <si>
-    <t>PUT DLTR</t>
+    <t>CALL NBIS APPLIED DIGITAL CORPORATION NEBIUS GROUP N V</t>
+  </si>
+  <si>
+    <t>PUT CRWV NAVITAS SEMICONDUCTOR CRPRTN COREWEAVE INC CLASS A</t>
+  </si>
+  <si>
+    <t>PUT CRWV COREWEAVE INC CLASS A COREWEAVE INC CLASS A</t>
+  </si>
+  <si>
+    <t>CALL CRWV COREWEAVE INC CLASS A COREWEAVE INC CLASS A</t>
+  </si>
+  <si>
+    <t>PUT DLTR COREWEAVE INC CLASS A DOLLAR TREE INC</t>
   </si>
   <si>
     <t>DOLLAR TREE INC</t>
   </si>
   <si>
-    <t>PUT DLTR DOLLAR TREE INC</t>
+    <t>PUT DLTR DOLLAR TREE INC DOLLAR TREE INC</t>
+  </si>
+  <si>
+    <t>PUT RGTI DOLLAR TREE INC RIGETTI COMPUTING INC</t>
+  </si>
+  <si>
+    <t>PUT META RIGETTI COMPUTING INC META PLATFORMS INC CL A</t>
+  </si>
+  <si>
+    <t>PUT PLTR META PLATFORMS INC CL A PALANTIR TECHNOLOGIES INC CL</t>
+  </si>
+  <si>
+    <t>CALL OPEN PALANTIR TECHNOLOGIES INC CL OPENDOOR TECHNOLOGIES INC</t>
+  </si>
+  <si>
+    <t>CALL NBIS OPENDOOR TECHNOLOGIES INC NEBIUS GROUP N V</t>
+  </si>
+  <si>
+    <t>PUT QQQ NEBIUS GROUP N V INVESCO QQQ TRUST SERIES 1</t>
+  </si>
+  <si>
+    <t>PUT NVDA INVESCO QQQ TRUST SERIES 1 NVIDIA CORPORATION</t>
+  </si>
+  <si>
+    <t>NVIDIA CORPORATION</t>
+  </si>
+  <si>
+    <t>PUT PLTR PALANTIR TECHNOLOGIES INC CL PALANTIR TECHNOLOGIES INC CL</t>
+  </si>
+  <si>
+    <t>PUT RGTI PALANTIR TECHNOLOGIES INC CL RIGETTI COMPUTING INC</t>
+  </si>
+  <si>
+    <t>CALL GLXY RIGETTI COMPUTING INC GALAXY DIGITAL INC CL A</t>
+  </si>
+  <si>
+    <t>CALL SNAP GALAXY DIGITAL INC CL A SNAP INC</t>
+  </si>
+  <si>
+    <t>PUT SPY SNAP INC STANDARD &amp; POORS DEPOSITORY</t>
+  </si>
+  <si>
+    <t>PUT BABA STANDARD &amp; POORS DEPOSITORY ALIBABA GROUP HOLDING LIMITE</t>
+  </si>
+  <si>
+    <t>CALL APLD ALIBABA GROUP HOLDING LIMITE APPLIED DIGITAL CORPORATION</t>
+  </si>
+  <si>
+    <t>PUT TSLA APPLIED DIGITAL CORPORATION TESLA INC</t>
+  </si>
+  <si>
+    <t>PUT TSLA TESLA INC TESLA INC</t>
+  </si>
+  <si>
+    <t>PUT TSLA TESLA INC</t>
+  </si>
+  <si>
+    <t>PUT CRWV TESLA INC COREWEAVE INC CLASS A</t>
+  </si>
+  <si>
+    <t>CALL AMD COREWEAVE INC CLASS A ADVANCED MICRO DEVICES INC</t>
+  </si>
+  <si>
+    <t>PUT QBTS COREWEAVE INC CLASS A D WAVE QUANTUM INC</t>
+  </si>
+  <si>
+    <t>CALL RKT D WAVE QUANTUM INC ROCKET COMPANIES INC CL A</t>
+  </si>
+  <si>
+    <t>PUT CRWV ROCKET COMPANIES INC CL A COREWEAVE INC CLASS A</t>
+  </si>
+  <si>
+    <t>CALL GOOG COREWEAVE INC CLASS A ALPHABET INC CLASS C</t>
+  </si>
+  <si>
+    <t>CALL GOOG ALPHABET INC CLASS C ALPHABET INC CLASS C</t>
+  </si>
+  <si>
+    <t>CALL NBIS ALPHABET INC CLASS C NEBIUS GROUP N V</t>
+  </si>
+  <si>
+    <t>PUT NBIS NEBIUS GROUP N V NEBIUS GROUP N V</t>
+  </si>
+  <si>
+    <t>PUT NVDA PALANTIR TECHNOLOGIES INC CL</t>
+  </si>
+  <si>
+    <t>CALL CRWV TESLA INC</t>
+  </si>
+  <si>
+    <t>CALL TSLA TESLA INC TESLA INC</t>
+  </si>
+  <si>
+    <t>CALL SPY TESLA INC STANDARD &amp; POORS DEPOSITORY</t>
+  </si>
+  <si>
+    <t>CALL APLD STANDARD &amp; POORS DEPOSITORY APPLIED DIGITAL CORPORATION</t>
+  </si>
+  <si>
+    <t>PUT NBIS APPLIED DIGITAL CORPORATION NEBIUS GROUP N V</t>
+  </si>
+  <si>
+    <t>CALL RKLB NEBIUS GROUP N V ROCKET LAB CORPORATION</t>
+  </si>
+  <si>
+    <t>ROCKET LAB CORPORATION</t>
+  </si>
+  <si>
+    <t>CALL RKLB ROCKET LAB CORPORATION ROCKET LAB CORPORATION</t>
+  </si>
+  <si>
+    <t>CALL AVGO ROCKET LAB CORPORATION BROADCOM INC</t>
+  </si>
+  <si>
+    <t>CALL OPEN BROADCOM INC OPENDOOR TECHNOLOGIES INC</t>
+  </si>
+  <si>
+    <t>PUT RGTI OPENDOOR TECHNOLOGIES INC RIGETTI COMPUTING INC</t>
+  </si>
+  <si>
+    <t>PUT PLTR RIGETTI COMPUTING INC PALANTIR TECHNOLOGIES INC CL</t>
+  </si>
+  <si>
+    <t>CALL UUUU RIGETTI COMPUTING INC ENERGY FUELS INC</t>
+  </si>
+  <si>
+    <t>ENERGY FUELS INC</t>
+  </si>
+  <si>
+    <t>CALL AAPL ENERGY FUELS INC APPLE INC</t>
+  </si>
+  <si>
+    <t>PUT CRWV APPLE INC COREWEAVE INC CLASS A</t>
+  </si>
+  <si>
+    <t>PUT AAPL COREWEAVE INC CLASS A APPLE INC</t>
+  </si>
+  <si>
+    <t>APPLE INC</t>
+  </si>
+  <si>
+    <t>CALL BYND APPLE INC BEYOND MEAT INC</t>
+  </si>
+  <si>
+    <t>BEYOND MEAT INC</t>
+  </si>
+  <si>
+    <t>CALL BYND BEYOND MEAT INC BEYOND MEAT INC</t>
+  </si>
+  <si>
+    <t>CALL RKT BEYOND MEAT INC ROCKET COMPANIES INC CL A</t>
+  </si>
+  <si>
+    <t>ROCKET COMPANIES INC CL A</t>
+  </si>
+  <si>
+    <t>PUT AMD ROCKET COMPANIES INC CL A ADVANCED MICRO DEVICES INC</t>
+  </si>
+  <si>
+    <t>CALL GLXY ADVANCED MICRO DEVICES INC GALAXY DIGITAL INC CL A</t>
+  </si>
+  <si>
+    <t>PUT NBIS GALAXY DIGITAL INC CL A NEBIUS GROUP N V</t>
+  </si>
+  <si>
+    <t>CALL GOOG NEBIUS GROUP N V ALPHABET INC CLASS C</t>
+  </si>
+  <si>
+    <t>ALPHABET INC CLASS C</t>
+  </si>
+  <si>
+    <t>PUT META ALPHABET INC CLASS C META PLATFORMS INC CL A</t>
+  </si>
+  <si>
+    <t>META PLATFORMS INC CL A</t>
+  </si>
+  <si>
+    <t>CALL MSFT META PLATFORMS INC CL A MICROSOFT CORP</t>
+  </si>
+  <si>
+    <t>PUT NVDA MICROSOFT CORP NVIDIA CORPORATION</t>
   </si>
   <si>
     <t>PUT RGTI RIGETTI COMPUTING INC</t>
   </si>
   <si>
-    <t>PUT QQQ INVESCO QQQ TRUST SERIES 1</t>
-  </si>
-  <si>
-    <t>NVIDIA CORPORATION</t>
-  </si>
-  <si>
-    <t>PALANTIR</t>
-  </si>
-  <si>
-    <t>CALL SNAP SNAP INC</t>
-  </si>
-  <si>
-    <t>PUT SPY STANDARD &amp; POORS DEPOSITORY</t>
-  </si>
-  <si>
-    <t>PUT BABA ALIBABA GROUP HOLDING LIMITE</t>
-  </si>
-  <si>
-    <t>PUT TSLA TESLA INC</t>
-  </si>
-  <si>
-    <t>TESLA INC PUT TSLA 45905 315</t>
-  </si>
-  <si>
-    <t>CALL RKT ROCKET COMPANIES INC CL A</t>
-  </si>
-  <si>
-    <t>CALL CRWV</t>
-  </si>
-  <si>
-    <t>CALL TSLA TESLA INC</t>
-  </si>
-  <si>
-    <t>CALL SPY STANDARD &amp; POORS DEPOSITORY</t>
-  </si>
-  <si>
-    <t>CALL RKLB</t>
-  </si>
-  <si>
-    <t>ROCKET LAB CORPORATION</t>
-  </si>
-  <si>
-    <t>OPENDOOR</t>
-  </si>
-  <si>
-    <t>CALL UUUU</t>
-  </si>
-  <si>
-    <t>ENERGY FUELS INC</t>
-  </si>
-  <si>
-    <t>CALL AAPL APPLE INC</t>
-  </si>
-  <si>
-    <t>PUT AAPL</t>
-  </si>
-  <si>
-    <t>APPLE INC</t>
-  </si>
-  <si>
-    <t>CALL BYND</t>
-  </si>
-  <si>
-    <t>BEYOND MEAT INC</t>
-  </si>
-  <si>
-    <t>CALL BYND BEYOND MEAT INC</t>
-  </si>
-  <si>
-    <t>CALL RKT</t>
-  </si>
-  <si>
-    <t>ROCKET COMPANIES INC CL A</t>
-  </si>
-  <si>
-    <t>PUT AMD ADVANCED MICRO DEVICES INC</t>
-  </si>
-  <si>
-    <t>PUT NBIS NEBIUS GROUP N V</t>
-  </si>
-  <si>
-    <t>CALL GOOG</t>
-  </si>
-  <si>
-    <t>ALPHABET INC CLASS C</t>
-  </si>
-  <si>
-    <t>PUT META</t>
-  </si>
-  <si>
-    <t>META PLATFORMS INC CL A</t>
-  </si>
-  <si>
-    <t>CALL MSFT MICROSOFT CORP</t>
-  </si>
-  <si>
-    <t>PUT MSTR</t>
-  </si>
-  <si>
-    <t>CALL ASTS</t>
-  </si>
-  <si>
-    <t>CALL ASTS AST SPACEMOBILE INC ADJ 3:1 STOCK SPLIT</t>
-  </si>
-  <si>
-    <t>CALL MU</t>
-  </si>
-  <si>
-    <t>CALL PANW</t>
+    <t>PUT MSTR RIGETTI COMPUTING INC</t>
+  </si>
+  <si>
+    <t>CALL ASTS RIGETTI COMPUTING INC</t>
+  </si>
+  <si>
+    <t>CALL ASTS RIGETTI COMPUTING INC AST SPACEMOBILE INC ADJ 3:1 STOCK SPLIT</t>
+  </si>
+  <si>
+    <t>CALL ASTS ADJ 3:1 STOCK SPLIT</t>
+  </si>
+  <si>
+    <t>ADJ 3:1 STOCK SPLIT</t>
+  </si>
+  <si>
+    <t>CALL MU ADJ 3:1 STOCK SPLIT</t>
+  </si>
+  <si>
+    <t>PUT META ADJ 3:1 STOCK SPLIT META PLATFORMS INC CL A</t>
+  </si>
+  <si>
+    <t>CALL PANW META PLATFORMS INC CL A PALO ALTO NETWORKS INC</t>
   </si>
   <si>
     <t>PALO ALTO NETWORKS INC</t>
@@ -346,103 +505,262 @@
     <t>ADJ 2:1 STOCK SPLIT</t>
   </si>
   <si>
-    <t>PUT AAPL APPLE INC</t>
-  </si>
-  <si>
-    <t>PUT AFRM AFFIRM HOLDINGS INC CL A</t>
-  </si>
-  <si>
-    <t>PUT ASTS AST SPACEMOBILE INC</t>
-  </si>
-  <si>
-    <t>CALL AVGO</t>
+    <t>PUT AAPL ADJ 2:1 STOCK SPLIT APPLE INC</t>
+  </si>
+  <si>
+    <t>PUT AAPL APPLE INC APPLE INC</t>
+  </si>
+  <si>
+    <t>PUT AFRM APPLE INC AFFIRM HOLDINGS INC CL A</t>
+  </si>
+  <si>
+    <t>PUT PLTR AFFIRM HOLDINGS INC CL A PALANTIR TECHNOLOGIES INC CL</t>
+  </si>
+  <si>
+    <t>PUT ASTS PALANTIR TECHNOLOGIES INC CL AST SPACEMOBILE INC</t>
+  </si>
+  <si>
+    <t>CALL AVGO AST SPACEMOBILE INC BROADCOM INC</t>
   </si>
   <si>
     <t>BROADCOM INC</t>
   </si>
   <si>
-    <t>CALL PANW PALO ALTO NETWORKS INC ADJ 2:1 STOCK SPLIT</t>
-  </si>
-  <si>
-    <t>PUT MU</t>
+    <t>CALL PANW BROADCOM INC PALO ALTO NETWORKS INC ADJ 2:1 STOCK SPLIT</t>
+  </si>
+  <si>
+    <t>PUT MU ADJ 2:1 STOCK SPLIT MICRON TECHNOLOGY INC</t>
   </si>
   <si>
     <t>MICRON TECHNOLOGY INC</t>
   </si>
   <si>
-    <t>CALL CRWV COREWEAVE INC CLASS A ADJ CASH DISTRIBUTION</t>
-  </si>
-  <si>
-    <t>PUT OKLO OKLO INC CLASS A</t>
+    <t>CALL CRWV MICRON TECHNOLOGY INC COREWEAVE INC CLASS A ADJ CASH DISTRIBUTION</t>
+  </si>
+  <si>
+    <t>PUT NBIS ADJ CASH DISTRIBUTION NEBIUS GROUP N V</t>
+  </si>
+  <si>
+    <t>PUT AFRM NEBIUS GROUP N V AFFIRM HOLDINGS INC CL A</t>
+  </si>
+  <si>
+    <t>PUT OKLO AFFIRM HOLDINGS INC CL A OKLO INC CLASS A</t>
+  </si>
+  <si>
+    <t>CALL AMD OKLO INC CLASS A ADVANCED MICRO DEVICES INC</t>
+  </si>
+  <si>
+    <t>CALL ASTS ADVANCED MICRO DEVICES INC AST SPACEMOBILE INC</t>
   </si>
   <si>
     <t>AST SPACEMOBILE INC</t>
   </si>
   <si>
-    <t>PUT RKT</t>
-  </si>
-  <si>
-    <t>CALL NU NU HOLDINGS LTD</t>
-  </si>
-  <si>
-    <t>CALL PYPL</t>
+    <t>PUT AAPL AST SPACEMOBILE INC APPLE INC</t>
+  </si>
+  <si>
+    <t>CALL CRWV APPLE INC COREWEAVE INC CLASS A</t>
+  </si>
+  <si>
+    <t>CALL GLXY COREWEAVE INC CLASS A GALAXY DIGITAL INC CL A</t>
+  </si>
+  <si>
+    <t>CALL PANW GALAXY DIGITAL INC CL A PALO ALTO NETWORKS INC</t>
+  </si>
+  <si>
+    <t>PUT RKT PALO ALTO NETWORKS INC ROCKET COMPANIES INC CL A</t>
+  </si>
+  <si>
+    <t>PUT TSLA ROCKET COMPANIES INC CL A TESLA INC</t>
+  </si>
+  <si>
+    <t>CALL NBIS COREWEAVE INC CLASS A NEBIUS GROUP N V</t>
+  </si>
+  <si>
+    <t>PUT QBTS NEBIUS GROUP N V D WAVE QUANTUM INC</t>
+  </si>
+  <si>
+    <t>PUT RGTI D WAVE QUANTUM INC RIGETTI COMPUTING INC</t>
+  </si>
+  <si>
+    <t>PUT RGTI RIGETTI COMPUTING INC RIGETTI COMPUTING INC</t>
+  </si>
+  <si>
+    <t>CALL NU RIGETTI COMPUTING INC NU HOLDINGS LTD</t>
+  </si>
+  <si>
+    <t>PUT NVDA NU HOLDINGS LTD NVIDIA CORPORATION</t>
+  </si>
+  <si>
+    <t>CALL NBIS NVIDIA CORPORATION NEBIUS GROUP N V</t>
+  </si>
+  <si>
+    <t>PUT TSLA GALAXY DIGITAL INC CL A TESLA INC</t>
+  </si>
+  <si>
+    <t>CALL AMD TESLA INC ADVANCED MICRO DEVICES INC</t>
+  </si>
+  <si>
+    <t>PUT NBIS ADVANCED MICRO DEVICES INC NEBIUS GROUP N V</t>
+  </si>
+  <si>
+    <t>CALL RZLV NEBIUS GROUP N V REZOLVE AI PLC</t>
+  </si>
+  <si>
+    <t>CALL CRWV REZOLVE AI PLC COREWEAVE INC CLASS A</t>
+  </si>
+  <si>
+    <t>CALL PYPL OPENDOOR TECHNOLOGIES INC PAYPAL HOLDINGS INC</t>
   </si>
   <si>
     <t>PAYPAL HOLDINGS INC</t>
   </si>
   <si>
-    <t>CALL POET</t>
-  </si>
-  <si>
-    <t>CALL SMCI SUPER MICRO COMPUTER INC</t>
-  </si>
-  <si>
-    <t>CALL AAPL</t>
-  </si>
-  <si>
-    <t>CALL ASTS AST SPACEMOBILE INC</t>
-  </si>
-  <si>
-    <t>PUT CVNA</t>
+    <t>CALL OPEN PAYPAL HOLDINGS INC OPENDOOR TECHNOLOGIES INC</t>
+  </si>
+  <si>
+    <t>PUT NVDA GALAXY DIGITAL INC CL A</t>
+  </si>
+  <si>
+    <t>CALL OPEN NVIDIA CORPORATION OPENDOOR TECHNOLOGIES INC</t>
+  </si>
+  <si>
+    <t>PUT PLTR OPENDOOR TECHNOLOGIES INC</t>
+  </si>
+  <si>
+    <t>CALL POET OPENDOOR TECHNOLOGIES INC</t>
+  </si>
+  <si>
+    <t>CALL SMCI RIGETTI COMPUTING INC SUPER MICRO COMPUTER INC</t>
+  </si>
+  <si>
+    <t>PUT TSLA SUPER MICRO COMPUTER INC TESLA INC</t>
+  </si>
+  <si>
+    <t>CALL AAPL TESLA INC APPLE INC</t>
+  </si>
+  <si>
+    <t>CALL ASTS APPLE INC AST SPACEMOBILE INC</t>
+  </si>
+  <si>
+    <t>CALL ASTS AST SPACEMOBILE INC AST SPACEMOBILE INC</t>
+  </si>
+  <si>
+    <t>PUT CVNA AST SPACEMOBILE INC CARVANA COMPANY</t>
   </si>
   <si>
     <t>CARVANA COMPANY</t>
   </si>
   <si>
+    <t>PUT PLTR CARVANA COMPANY PALANTIR TECHNOLOGIES INC CL</t>
+  </si>
+  <si>
+    <t>CALL POET PALANTIR TECHNOLOGIES INC CL POET TECHNOLOGIES INC</t>
+  </si>
+  <si>
     <t>POET TECHNOLOGIES INC</t>
   </si>
   <si>
-    <t>CALL APLD APPLIED DIGITAL CORPORATION</t>
-  </si>
-  <si>
-    <t>CALL NVDA</t>
-  </si>
-  <si>
-    <t>CALL RKLB ROCKET LAB CORPORATION</t>
-  </si>
-  <si>
-    <t>CALL WBD WARNER BROS DISCOVERY INC</t>
-  </si>
-  <si>
-    <t>PUT MU MICRON TECHNOLOGY INC</t>
-  </si>
-  <si>
-    <t>MICRON TECHNOLOGY INC CALL MU 46017 295</t>
-  </si>
-  <si>
-    <t>CALL MSFT</t>
-  </si>
-  <si>
-    <t>MICROSOFT</t>
-  </si>
-  <si>
-    <t>CALL TSLA</t>
-  </si>
-  <si>
-    <t>PUT NVDA NVIDIA CORPORATION ADJ 10:1 STOCK SPLIT</t>
-  </si>
-  <si>
-    <t>CALL NVDA NVIDIA CORPORATION ADJ 10:1 STOCK SPLIT</t>
+    <t>PUT TSLA POET TECHNOLOGIES INC TESLA INC</t>
+  </si>
+  <si>
+    <t>CALL APLD TESLA INC APPLIED DIGITAL CORPORATION</t>
+  </si>
+  <si>
+    <t>PUT META APPLIED DIGITAL CORPORATION META PLATFORMS INC CL A</t>
+  </si>
+  <si>
+    <t>PUT NBIS META PLATFORMS INC CL A NEBIUS GROUP N V</t>
+  </si>
+  <si>
+    <t>PUT META NEBIUS GROUP N V META PLATFORMS INC CL A</t>
+  </si>
+  <si>
+    <t>CALL NBIS META PLATFORMS INC CL A NEBIUS GROUP N V</t>
+  </si>
+  <si>
+    <t>CALL RKLB NAVITAS SEMICONDUCTOR CRPRTN ROCKET LAB CORPORATION</t>
+  </si>
+  <si>
+    <t>PUT NVDA ROCKET LAB CORPORATION NVIDIA CORPORATION</t>
+  </si>
+  <si>
+    <t>CALL NVDA NVIDIA CORPORATION NVIDIA CORPORATION</t>
+  </si>
+  <si>
+    <t>CALL NBIS PALANTIR TECHNOLOGIES INC CL NEBIUS GROUP N V</t>
+  </si>
+  <si>
+    <t>CALL APLD NEBIUS GROUP N V APPLIED DIGITAL CORPORATION</t>
+  </si>
+  <si>
+    <t>CALL APLD APPLIED DIGITAL CORPORATION APPLIED DIGITAL CORPORATION</t>
+  </si>
+  <si>
+    <t>PUT PLTR APPLIED DIGITAL CORPORATION PALANTIR TECHNOLOGIES INC CL</t>
+  </si>
+  <si>
+    <t>CALL RKLB PALANTIR TECHNOLOGIES INC CL ROCKET LAB CORPORATION</t>
+  </si>
+  <si>
+    <t>CALL WBD ROCKET LAB CORPORATION WARNER BROS DISCOVERY INC</t>
+  </si>
+  <si>
+    <t>PUT MU WARNER BROS DISCOVERY INC MICRON TECHNOLOGY INC</t>
+  </si>
+  <si>
+    <t>CALL MU MICRON TECHNOLOGY INC MICRON TECHNOLOGY INC</t>
+  </si>
+  <si>
+    <t>PUT AAPL RIGETTI COMPUTING INC APPLE INC</t>
+  </si>
+  <si>
+    <t>PUT RGTI COREWEAVE INC CLASS A RIGETTI COMPUTING INC</t>
+  </si>
+  <si>
+    <t>CALL AAPL RIGETTI COMPUTING INC APPLE INC</t>
+  </si>
+  <si>
+    <t>CALL MSFT APPLE INC MICROSOFT CORP</t>
+  </si>
+  <si>
+    <t>CALL MSFT MICROSOFT CORP MICROSOFT CORP</t>
+  </si>
+  <si>
+    <t>PUT NBIS MICROSOFT CORP NEBIUS GROUP N V</t>
+  </si>
+  <si>
+    <t>PUT TSLA NVIDIA CORPORATION TESLA INC</t>
+  </si>
+  <si>
+    <t>PUT PLTR TESLA INC PALANTIR TECHNOLOGIES INC CL</t>
+  </si>
+  <si>
+    <t>PUT MSFT PALANTIR TECHNOLOGIES INC CL MICROSOFT CORP</t>
+  </si>
+  <si>
+    <t>CALL RKLB MICROSOFT CORP ROCKET LAB CORPORATION</t>
+  </si>
+  <si>
+    <t>PUT PLTR ROCKET LAB CORPORATION PALANTIR TECHNOLOGIES INC CL</t>
+  </si>
+  <si>
+    <t>CALL TSLA PALANTIR TECHNOLOGIES INC CL TESLA INC</t>
+  </si>
+  <si>
+    <t>CALL ASTS TESLA INC AST SPACEMOBILE INC</t>
+  </si>
+  <si>
+    <t>PUT NVDA AST SPACEMOBILE INC NVIDIA CORPORATION ADJ 10:1 STOCK SPLIT</t>
+  </si>
+  <si>
+    <t>CALL NVDA ADJ 10:1 STOCK SPLIT NVIDIA CORPORATION ADJ 10:1 STOCK SPLIT</t>
+  </si>
+  <si>
+    <t>PUT NVDA ADJ 10:1 STOCK SPLIT NVIDIA CORPORATION</t>
+  </si>
+  <si>
+    <t>PUT NVDA NVIDIA CORPORATION NVIDIA CORPORATION</t>
   </si>
   <si>
     <t>08/15/2025</t>
@@ -1137,10 +1455,10 @@
         <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>143</v>
+        <v>249</v>
       </c>
       <c r="H2" t="s">
-        <v>180</v>
+        <v>286</v>
       </c>
       <c r="K2">
         <v>602.61</v>
@@ -1160,10 +1478,10 @@
         <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>144</v>
+        <v>250</v>
       </c>
       <c r="H3" t="s">
-        <v>184</v>
+        <v>290</v>
       </c>
       <c r="K3">
         <v>517.33</v>
@@ -1183,10 +1501,10 @@
         <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>144</v>
+        <v>250</v>
       </c>
       <c r="H4" t="s">
-        <v>152</v>
+        <v>258</v>
       </c>
       <c r="K4">
         <v>513.3099999999999</v>
@@ -1206,10 +1524,10 @@
         <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>144</v>
+        <v>250</v>
       </c>
       <c r="H5" t="s">
-        <v>152</v>
+        <v>258</v>
       </c>
       <c r="K5">
         <v>349.99</v>
@@ -1229,10 +1547,10 @@
         <v>18</v>
       </c>
       <c r="G6" t="s">
-        <v>145</v>
+        <v>251</v>
       </c>
       <c r="H6" t="s">
-        <v>223</v>
+        <v>329</v>
       </c>
       <c r="K6">
         <v>281.63</v>
@@ -1252,10 +1570,10 @@
         <v>19</v>
       </c>
       <c r="G7" t="s">
-        <v>146</v>
+        <v>252</v>
       </c>
       <c r="H7" t="s">
-        <v>231</v>
+        <v>337</v>
       </c>
       <c r="K7">
         <v>991.6799999999999</v>
@@ -1275,10 +1593,10 @@
         <v>20</v>
       </c>
       <c r="G8" t="s">
-        <v>147</v>
+        <v>253</v>
       </c>
       <c r="H8" t="s">
-        <v>232</v>
+        <v>338</v>
       </c>
       <c r="K8">
         <v>99.34</v>
@@ -1298,10 +1616,10 @@
         <v>21</v>
       </c>
       <c r="G9" t="s">
-        <v>147</v>
+        <v>253</v>
       </c>
       <c r="H9" t="s">
-        <v>229</v>
+        <v>335</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -1318,13 +1636,13 @@
     </row>
     <row r="10" spans="1:15">
       <c r="F10" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G10" t="s">
-        <v>148</v>
+        <v>254</v>
       </c>
       <c r="H10" t="s">
-        <v>229</v>
+        <v>335</v>
       </c>
       <c r="K10">
         <v>483.36</v>
@@ -1341,13 +1659,13 @@
     </row>
     <row r="11" spans="1:15">
       <c r="F11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G11" t="s">
-        <v>148</v>
+        <v>254</v>
       </c>
       <c r="H11" t="s">
-        <v>229</v>
+        <v>335</v>
       </c>
       <c r="K11">
         <v>886.6799999999999</v>
@@ -1364,13 +1682,13 @@
     </row>
     <row r="12" spans="1:15">
       <c r="F12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G12" t="s">
-        <v>148</v>
+        <v>254</v>
       </c>
       <c r="H12" t="s">
-        <v>229</v>
+        <v>335</v>
       </c>
       <c r="K12">
         <v>96.33</v>
@@ -1387,13 +1705,13 @@
     </row>
     <row r="13" spans="1:15">
       <c r="F13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G13" t="s">
-        <v>148</v>
+        <v>254</v>
       </c>
       <c r="H13" t="s">
-        <v>229</v>
+        <v>335</v>
       </c>
       <c r="K13">
         <v>357.34</v>
@@ -1410,13 +1728,13 @@
     </row>
     <row r="14" spans="1:15">
       <c r="F14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G14" t="s">
-        <v>148</v>
+        <v>254</v>
       </c>
       <c r="H14" t="s">
-        <v>229</v>
+        <v>335</v>
       </c>
       <c r="K14">
         <v>96.34</v>
@@ -1433,13 +1751,13 @@
     </row>
     <row r="15" spans="1:15">
       <c r="F15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G15" t="s">
-        <v>148</v>
+        <v>254</v>
       </c>
       <c r="H15" t="s">
-        <v>229</v>
+        <v>335</v>
       </c>
       <c r="K15">
         <v>893.36</v>
@@ -1456,13 +1774,13 @@
     </row>
     <row r="16" spans="1:15">
       <c r="F16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G16" t="s">
-        <v>146</v>
+        <v>252</v>
       </c>
       <c r="H16" t="s">
-        <v>231</v>
+        <v>337</v>
       </c>
       <c r="K16">
         <v>73.01000000000001</v>
@@ -1479,13 +1797,13 @@
     </row>
     <row r="17" spans="6:15">
       <c r="F17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G17" t="s">
-        <v>144</v>
+        <v>250</v>
       </c>
       <c r="H17" t="s">
-        <v>184</v>
+        <v>290</v>
       </c>
       <c r="K17">
         <v>326.66</v>
@@ -1502,13 +1820,13 @@
     </row>
     <row r="18" spans="6:15">
       <c r="F18" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G18" t="s">
-        <v>149</v>
+        <v>255</v>
       </c>
       <c r="H18" t="s">
-        <v>227</v>
+        <v>333</v>
       </c>
       <c r="K18">
         <v>56.66</v>
@@ -1525,13 +1843,13 @@
     </row>
     <row r="19" spans="6:15">
       <c r="F19" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G19" t="s">
-        <v>150</v>
+        <v>256</v>
       </c>
       <c r="H19" t="s">
-        <v>198</v>
+        <v>304</v>
       </c>
       <c r="K19">
         <v>77.3</v>
@@ -1548,13 +1866,13 @@
     </row>
     <row r="20" spans="6:15">
       <c r="F20" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G20" t="s">
-        <v>151</v>
+        <v>257</v>
       </c>
       <c r="H20" t="s">
-        <v>150</v>
+        <v>256</v>
       </c>
       <c r="K20">
         <v>697.3</v>
@@ -1571,13 +1889,13 @@
     </row>
     <row r="21" spans="6:15">
       <c r="F21" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G21" t="s">
-        <v>152</v>
+        <v>258</v>
       </c>
       <c r="H21" t="s">
-        <v>191</v>
+        <v>297</v>
       </c>
       <c r="K21">
         <v>115.33</v>
@@ -1594,13 +1912,13 @@
     </row>
     <row r="22" spans="6:15">
       <c r="F22" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G22" t="s">
-        <v>152</v>
+        <v>258</v>
       </c>
       <c r="H22" t="s">
-        <v>191</v>
+        <v>297</v>
       </c>
       <c r="K22">
         <v>17.33</v>
@@ -1617,13 +1935,13 @@
     </row>
     <row r="23" spans="6:15">
       <c r="F23" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G23" t="s">
-        <v>153</v>
+        <v>259</v>
       </c>
       <c r="H23" t="s">
-        <v>155</v>
+        <v>261</v>
       </c>
       <c r="K23">
         <v>609.33</v>
@@ -1643,10 +1961,10 @@
         <v>21</v>
       </c>
       <c r="G24" t="s">
-        <v>153</v>
+        <v>259</v>
       </c>
       <c r="H24" t="s">
-        <v>155</v>
+        <v>261</v>
       </c>
       <c r="K24">
         <v>574.33</v>
@@ -1663,13 +1981,13 @@
     </row>
     <row r="25" spans="6:15">
       <c r="F25" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G25" t="s">
-        <v>154</v>
+        <v>260</v>
       </c>
       <c r="H25" t="s">
-        <v>143</v>
+        <v>249</v>
       </c>
       <c r="K25">
         <v>683.26</v>
@@ -1686,13 +2004,13 @@
     </row>
     <row r="26" spans="6:15">
       <c r="F26" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G26" t="s">
-        <v>155</v>
+        <v>261</v>
       </c>
       <c r="H26" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="K26">
         <v>218.65</v>
@@ -1709,13 +2027,13 @@
     </row>
     <row r="27" spans="6:15">
       <c r="F27" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G27" t="s">
-        <v>155</v>
+        <v>261</v>
       </c>
       <c r="H27" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="K27">
         <v>240.65</v>
@@ -1732,13 +2050,13 @@
     </row>
     <row r="28" spans="6:15">
       <c r="F28" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G28" t="s">
-        <v>156</v>
+        <v>262</v>
       </c>
       <c r="H28" t="s">
-        <v>172</v>
+        <v>278</v>
       </c>
       <c r="K28">
         <v>448.65</v>
@@ -1755,13 +2073,13 @@
     </row>
     <row r="29" spans="6:15">
       <c r="F29" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G29" t="s">
-        <v>155</v>
+        <v>261</v>
       </c>
       <c r="H29" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="K29">
         <v>247.33</v>
@@ -1781,10 +2099,10 @@
         <v>21</v>
       </c>
       <c r="G30" t="s">
-        <v>155</v>
+        <v>261</v>
       </c>
       <c r="H30" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="K30">
         <v>538.65</v>
@@ -1804,10 +2122,10 @@
         <v>21</v>
       </c>
       <c r="G31" t="s">
-        <v>155</v>
+        <v>261</v>
       </c>
       <c r="H31" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="K31">
         <v>284.33</v>
@@ -1827,10 +2145,10 @@
         <v>21</v>
       </c>
       <c r="G32" t="s">
-        <v>157</v>
+        <v>263</v>
       </c>
       <c r="H32" t="s">
-        <v>154</v>
+        <v>260</v>
       </c>
       <c r="K32">
         <v>83.65000000000001</v>
@@ -1850,10 +2168,10 @@
         <v>21</v>
       </c>
       <c r="G33" t="s">
-        <v>157</v>
+        <v>263</v>
       </c>
       <c r="H33" t="s">
-        <v>154</v>
+        <v>260</v>
       </c>
       <c r="K33">
         <v>289.95</v>
@@ -1870,13 +2188,13 @@
     </row>
     <row r="34" spans="6:15">
       <c r="F34" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G34" t="s">
-        <v>158</v>
+        <v>264</v>
       </c>
       <c r="H34" t="s">
-        <v>213</v>
+        <v>319</v>
       </c>
       <c r="K34">
         <v>991.01</v>
@@ -1893,13 +2211,13 @@
     </row>
     <row r="35" spans="6:15">
       <c r="F35" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G35" t="s">
-        <v>158</v>
+        <v>264</v>
       </c>
       <c r="H35" t="s">
-        <v>213</v>
+        <v>319</v>
       </c>
       <c r="K35">
         <v>898.67</v>
@@ -1916,13 +2234,13 @@
     </row>
     <row r="36" spans="6:15">
       <c r="F36" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G36" t="s">
-        <v>158</v>
+        <v>264</v>
       </c>
       <c r="H36" t="s">
-        <v>214</v>
+        <v>320</v>
       </c>
       <c r="K36">
         <v>796.6799999999999</v>
@@ -1939,13 +2257,13 @@
     </row>
     <row r="37" spans="6:15">
       <c r="F37" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G37" t="s">
-        <v>159</v>
+        <v>265</v>
       </c>
       <c r="H37" t="s">
-        <v>160</v>
+        <v>266</v>
       </c>
       <c r="K37">
         <v>2153.33</v>
@@ -1965,10 +2283,10 @@
         <v>21</v>
       </c>
       <c r="G38" t="s">
-        <v>159</v>
+        <v>265</v>
       </c>
       <c r="H38" t="s">
-        <v>160</v>
+        <v>266</v>
       </c>
       <c r="K38">
         <v>1020.66</v>
@@ -1985,13 +2303,13 @@
     </row>
     <row r="39" spans="6:15">
       <c r="F39" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G39" t="s">
-        <v>153</v>
+        <v>259</v>
       </c>
       <c r="H39" t="s">
-        <v>155</v>
+        <v>261</v>
       </c>
       <c r="K39">
         <v>548.65</v>
@@ -2008,13 +2326,13 @@
     </row>
     <row r="40" spans="6:15">
       <c r="F40" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G40" t="s">
-        <v>160</v>
+        <v>266</v>
       </c>
       <c r="H40" t="s">
-        <v>192</v>
+        <v>298</v>
       </c>
       <c r="K40">
         <v>353.31</v>
@@ -2031,13 +2349,13 @@
     </row>
     <row r="41" spans="6:15">
       <c r="F41" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G41" t="s">
-        <v>161</v>
+        <v>267</v>
       </c>
       <c r="H41" t="s">
-        <v>167</v>
+        <v>273</v>
       </c>
       <c r="K41">
         <v>343.31</v>
@@ -2054,13 +2372,13 @@
     </row>
     <row r="42" spans="6:15">
       <c r="F42" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G42" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="H42" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="K42">
         <v>411.99</v>
@@ -2077,13 +2395,13 @@
     </row>
     <row r="43" spans="6:15">
       <c r="F43" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G43" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="H43" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="K43">
         <v>318.66</v>
@@ -2100,13 +2418,13 @@
     </row>
     <row r="44" spans="6:15">
       <c r="F44" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G44" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="H44" t="s">
-        <v>160</v>
+        <v>266</v>
       </c>
       <c r="K44">
         <v>4823.31</v>
@@ -2123,13 +2441,13 @@
     </row>
     <row r="45" spans="6:15">
       <c r="F45" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G45" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="H45" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="K45">
         <v>86.34</v>
@@ -2146,13 +2464,13 @@
     </row>
     <row r="46" spans="6:15">
       <c r="F46" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G46" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="H46" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="K46">
         <v>2072.06</v>
@@ -2169,13 +2487,13 @@
     </row>
     <row r="47" spans="6:15">
       <c r="F47" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G47" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="H47" t="s">
-        <v>209</v>
+        <v>315</v>
       </c>
       <c r="K47">
         <v>31.34</v>
@@ -2192,13 +2510,13 @@
     </row>
     <row r="48" spans="6:15">
       <c r="F48" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G48" t="s">
-        <v>155</v>
+        <v>261</v>
       </c>
       <c r="H48" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="K48">
         <v>543.33</v>
@@ -2215,13 +2533,13 @@
     </row>
     <row r="49" spans="6:15">
       <c r="F49" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G49" t="s">
-        <v>155</v>
+        <v>261</v>
       </c>
       <c r="H49" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="K49">
         <v>659.33</v>
@@ -2238,13 +2556,13 @@
     </row>
     <row r="50" spans="6:15">
       <c r="F50" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G50" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="H50" t="s">
-        <v>157</v>
+        <v>263</v>
       </c>
       <c r="K50">
         <v>479.33</v>
@@ -2261,13 +2579,13 @@
     </row>
     <row r="51" spans="6:15">
       <c r="F51" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G51" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="H51" t="s">
-        <v>157</v>
+        <v>263</v>
       </c>
       <c r="K51">
         <v>402.33</v>
@@ -2284,13 +2602,13 @@
     </row>
     <row r="52" spans="6:15">
       <c r="F52" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G52" t="s">
-        <v>166</v>
+        <v>272</v>
       </c>
       <c r="H52" t="s">
-        <v>224</v>
+        <v>330</v>
       </c>
       <c r="K52">
         <v>98.65000000000001</v>
@@ -2307,13 +2625,13 @@
     </row>
     <row r="53" spans="6:15">
       <c r="F53" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G53" t="s">
-        <v>166</v>
+        <v>272</v>
       </c>
       <c r="H53" t="s">
-        <v>224</v>
+        <v>330</v>
       </c>
       <c r="K53">
         <v>98.65000000000001</v>
@@ -2330,13 +2648,13 @@
     </row>
     <row r="54" spans="6:15">
       <c r="F54" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G54" t="s">
-        <v>167</v>
+        <v>273</v>
       </c>
       <c r="H54" t="s">
-        <v>179</v>
+        <v>285</v>
       </c>
       <c r="K54">
         <v>1151.68</v>
@@ -2353,13 +2671,13 @@
     </row>
     <row r="55" spans="6:15">
       <c r="F55" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G55" t="s">
-        <v>167</v>
+        <v>273</v>
       </c>
       <c r="H55" t="s">
-        <v>179</v>
+        <v>285</v>
       </c>
       <c r="K55">
         <v>1571.68</v>
@@ -2376,13 +2694,13 @@
     </row>
     <row r="56" spans="6:15">
       <c r="F56" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G56" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="H56" t="s">
-        <v>176</v>
+        <v>282</v>
       </c>
       <c r="K56">
         <v>396.66</v>
@@ -2399,13 +2717,13 @@
     </row>
     <row r="57" spans="6:15">
       <c r="F57" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G57" t="s">
-        <v>167</v>
+        <v>273</v>
       </c>
       <c r="H57" t="s">
-        <v>179</v>
+        <v>285</v>
       </c>
       <c r="K57">
         <v>1471.68</v>
@@ -2422,13 +2740,13 @@
     </row>
     <row r="58" spans="6:15">
       <c r="F58" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G58" t="s">
-        <v>167</v>
+        <v>273</v>
       </c>
       <c r="H58" t="s">
-        <v>179</v>
+        <v>285</v>
       </c>
       <c r="K58">
         <v>1696.68</v>
@@ -2445,13 +2763,13 @@
     </row>
     <row r="59" spans="6:15">
       <c r="F59" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G59" t="s">
-        <v>168</v>
+        <v>274</v>
       </c>
       <c r="H59" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
       <c r="K59">
         <v>371.68</v>
@@ -2468,13 +2786,13 @@
     </row>
     <row r="60" spans="6:15">
       <c r="F60" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G60" t="s">
-        <v>168</v>
+        <v>274</v>
       </c>
       <c r="H60" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
       <c r="K60">
         <v>421.68</v>
@@ -2491,13 +2809,13 @@
     </row>
     <row r="61" spans="6:15">
       <c r="F61" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G61" t="s">
-        <v>168</v>
+        <v>274</v>
       </c>
       <c r="H61" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
       <c r="K61">
         <v>613.36</v>
@@ -2514,13 +2832,13 @@
     </row>
     <row r="62" spans="6:15">
       <c r="F62" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G62" t="s">
-        <v>168</v>
+        <v>274</v>
       </c>
       <c r="H62" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
       <c r="K62">
         <v>1076.68</v>
@@ -2537,13 +2855,13 @@
     </row>
     <row r="63" spans="6:15">
       <c r="F63" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G63" t="s">
-        <v>168</v>
+        <v>274</v>
       </c>
       <c r="H63" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
       <c r="K63">
         <v>616.6799999999999</v>
@@ -2560,13 +2878,13 @@
     </row>
     <row r="64" spans="6:15">
       <c r="F64" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="G64" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="H64" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="K64">
         <v>446.66</v>
@@ -2583,13 +2901,13 @@
     </row>
     <row r="65" spans="6:15">
       <c r="F65" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="G65" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="H65" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="K65">
         <v>256.66</v>
@@ -2606,13 +2924,13 @@
     </row>
     <row r="66" spans="6:15">
       <c r="F66" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="G66" t="s">
-        <v>159</v>
+        <v>265</v>
       </c>
       <c r="H66" t="s">
-        <v>160</v>
+        <v>266</v>
       </c>
       <c r="K66">
         <v>1015.99</v>
@@ -2629,13 +2947,13 @@
     </row>
     <row r="67" spans="6:15">
       <c r="F67" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="G67" t="s">
-        <v>159</v>
+        <v>265</v>
       </c>
       <c r="H67" t="s">
-        <v>160</v>
+        <v>266</v>
       </c>
       <c r="K67">
         <v>673.33</v>
@@ -2652,13 +2970,13 @@
     </row>
     <row r="68" spans="6:15">
       <c r="F68" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G68" t="s">
-        <v>168</v>
+        <v>274</v>
       </c>
       <c r="H68" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
       <c r="K68">
         <v>322.67</v>
@@ -2675,13 +2993,13 @@
     </row>
     <row r="69" spans="6:15">
       <c r="F69" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G69" t="s">
-        <v>168</v>
+        <v>274</v>
       </c>
       <c r="H69" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
       <c r="K69">
         <v>846.6799999999999</v>
@@ -2698,13 +3016,13 @@
     </row>
     <row r="70" spans="6:15">
       <c r="F70" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G70" t="s">
-        <v>168</v>
+        <v>274</v>
       </c>
       <c r="H70" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
       <c r="K70">
         <v>801.6799999999999</v>
@@ -2721,13 +3039,13 @@
     </row>
     <row r="71" spans="6:15">
       <c r="F71" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="G71" t="s">
-        <v>169</v>
+        <v>275</v>
       </c>
       <c r="H71" t="s">
-        <v>196</v>
+        <v>302</v>
       </c>
       <c r="K71">
         <v>298.65</v>
@@ -2744,13 +3062,13 @@
     </row>
     <row r="72" spans="6:15">
       <c r="F72" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G72" t="s">
-        <v>170</v>
+        <v>276</v>
       </c>
       <c r="H72" t="s">
-        <v>189</v>
+        <v>295</v>
       </c>
       <c r="K72">
         <v>371.63</v>
@@ -2767,13 +3085,13 @@
     </row>
     <row r="73" spans="6:15">
       <c r="F73" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G73" t="s">
-        <v>170</v>
+        <v>276</v>
       </c>
       <c r="H73" t="s">
-        <v>189</v>
+        <v>295</v>
       </c>
       <c r="K73">
         <v>351.63</v>
@@ -2790,13 +3108,13 @@
     </row>
     <row r="74" spans="6:15">
       <c r="F74" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="G74" t="s">
-        <v>171</v>
+        <v>277</v>
       </c>
       <c r="H74" t="s">
-        <v>219</v>
+        <v>325</v>
       </c>
       <c r="K74">
         <v>498.65</v>
@@ -2813,13 +3131,13 @@
     </row>
     <row r="75" spans="6:15">
       <c r="F75" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G75" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="H75" t="s">
-        <v>176</v>
+        <v>282</v>
       </c>
       <c r="K75">
         <v>208.33</v>
@@ -2836,13 +3154,13 @@
     </row>
     <row r="76" spans="6:15">
       <c r="F76" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G76" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="H76" t="s">
-        <v>176</v>
+        <v>282</v>
       </c>
       <c r="K76">
         <v>381.99</v>
@@ -2859,13 +3177,13 @@
     </row>
     <row r="77" spans="6:15">
       <c r="F77" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G77" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="H77" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="K77">
         <v>498.66</v>
@@ -2882,13 +3200,13 @@
     </row>
     <row r="78" spans="6:15">
       <c r="F78" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G78" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="H78" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="K78">
         <v>597.99</v>
@@ -2905,13 +3223,13 @@
     </row>
     <row r="79" spans="6:15">
       <c r="F79" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G79" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="H79" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="K79">
         <v>548.66</v>
@@ -2928,13 +3246,13 @@
     </row>
     <row r="80" spans="6:15">
       <c r="F80" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G80" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="H80" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="K80">
         <v>402.33</v>
@@ -2951,13 +3269,13 @@
     </row>
     <row r="81" spans="6:15">
       <c r="F81" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G81" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="H81" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="K81">
         <v>880.66</v>
@@ -2974,13 +3292,13 @@
     </row>
     <row r="82" spans="6:15">
       <c r="F82" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="G82" t="s">
-        <v>172</v>
+        <v>278</v>
       </c>
       <c r="H82" t="s">
-        <v>153</v>
+        <v>259</v>
       </c>
       <c r="K82">
         <v>1099.33</v>
@@ -2997,13 +3315,13 @@
     </row>
     <row r="83" spans="6:15">
       <c r="F83" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="G83" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="H83" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="K83">
         <v>646.66</v>
@@ -3020,13 +3338,13 @@
     </row>
     <row r="84" spans="6:15">
       <c r="F84" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G84" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="H84" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="K84">
         <v>726.66</v>
@@ -3043,13 +3361,13 @@
     </row>
     <row r="85" spans="6:15">
       <c r="F85" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="G85" t="s">
-        <v>174</v>
+        <v>280</v>
       </c>
       <c r="H85" t="s">
-        <v>172</v>
+        <v>278</v>
       </c>
       <c r="K85">
         <v>379.33</v>
@@ -3066,13 +3384,13 @@
     </row>
     <row r="86" spans="6:15">
       <c r="F86" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G86" t="s">
-        <v>153</v>
+        <v>259</v>
       </c>
       <c r="H86" t="s">
-        <v>155</v>
+        <v>261</v>
       </c>
       <c r="K86">
         <v>348.65</v>
@@ -3089,13 +3407,13 @@
     </row>
     <row r="87" spans="6:15">
       <c r="F87" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G87" t="s">
-        <v>153</v>
+        <v>259</v>
       </c>
       <c r="H87" t="s">
-        <v>155</v>
+        <v>261</v>
       </c>
       <c r="K87">
         <v>977.3</v>
@@ -3112,13 +3430,13 @@
     </row>
     <row r="88" spans="6:15">
       <c r="F88" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G88" t="s">
-        <v>153</v>
+        <v>259</v>
       </c>
       <c r="H88" t="s">
-        <v>155</v>
+        <v>261</v>
       </c>
       <c r="K88">
         <v>398.65</v>
@@ -3135,13 +3453,13 @@
     </row>
     <row r="89" spans="6:15">
       <c r="F89" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="G89" t="s">
-        <v>175</v>
+        <v>281</v>
       </c>
       <c r="H89" t="s">
-        <v>226</v>
+        <v>332</v>
       </c>
       <c r="K89">
         <v>597.33</v>
@@ -3158,13 +3476,13 @@
     </row>
     <row r="90" spans="6:15">
       <c r="F90" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="G90" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="H90" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="K90">
         <v>298.66</v>
@@ -3181,13 +3499,13 @@
     </row>
     <row r="91" spans="6:15">
       <c r="F91" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G91" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="H91" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="K91">
         <v>226.66</v>
@@ -3204,13 +3522,13 @@
     </row>
     <row r="92" spans="6:15">
       <c r="F92" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G92" t="s">
-        <v>176</v>
+        <v>282</v>
       </c>
       <c r="H92" t="s">
-        <v>159</v>
+        <v>265</v>
       </c>
       <c r="K92">
         <v>129.33</v>
@@ -3227,13 +3545,13 @@
     </row>
     <row r="93" spans="6:15">
       <c r="F93" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="G93" t="s">
-        <v>177</v>
+        <v>283</v>
       </c>
       <c r="H93" t="s">
-        <v>207</v>
+        <v>313</v>
       </c>
       <c r="K93">
         <v>84.31999999999999</v>
@@ -3250,13 +3568,13 @@
     </row>
     <row r="94" spans="6:15">
       <c r="F94" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G94" t="s">
-        <v>177</v>
+        <v>283</v>
       </c>
       <c r="H94" t="s">
-        <v>207</v>
+        <v>313</v>
       </c>
       <c r="K94">
         <v>84.33</v>
@@ -3273,13 +3591,13 @@
     </row>
     <row r="95" spans="6:15">
       <c r="F95" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G95" t="s">
-        <v>177</v>
+        <v>283</v>
       </c>
       <c r="H95" t="s">
-        <v>224</v>
+        <v>330</v>
       </c>
       <c r="K95">
         <v>222.65</v>
@@ -3296,13 +3614,13 @@
     </row>
     <row r="96" spans="6:15">
       <c r="F96" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G96" t="s">
-        <v>177</v>
+        <v>283</v>
       </c>
       <c r="H96" t="s">
-        <v>224</v>
+        <v>330</v>
       </c>
       <c r="K96">
         <v>114.33</v>
@@ -3319,13 +3637,13 @@
     </row>
     <row r="97" spans="6:15">
       <c r="F97" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="G97" t="s">
-        <v>171</v>
+        <v>277</v>
       </c>
       <c r="H97" t="s">
-        <v>219</v>
+        <v>325</v>
       </c>
       <c r="K97">
         <v>454.32</v>
@@ -3342,13 +3660,13 @@
     </row>
     <row r="98" spans="6:15">
       <c r="F98" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="G98" t="s">
-        <v>176</v>
+        <v>282</v>
       </c>
       <c r="H98" t="s">
-        <v>159</v>
+        <v>265</v>
       </c>
       <c r="K98">
         <v>96.66</v>
@@ -3365,13 +3683,13 @@
     </row>
     <row r="99" spans="6:15">
       <c r="F99" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="G99" t="s">
-        <v>176</v>
+        <v>282</v>
       </c>
       <c r="H99" t="s">
-        <v>159</v>
+        <v>265</v>
       </c>
       <c r="K99">
         <v>162.66</v>
@@ -3388,13 +3706,13 @@
     </row>
     <row r="100" spans="6:15">
       <c r="F100" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="G100" t="s">
-        <v>178</v>
+        <v>284</v>
       </c>
       <c r="H100" t="s">
-        <v>182</v>
+        <v>288</v>
       </c>
       <c r="K100">
         <v>52.67</v>
@@ -3411,13 +3729,13 @@
     </row>
     <row r="101" spans="6:15">
       <c r="F101" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="G101" t="s">
-        <v>178</v>
+        <v>284</v>
       </c>
       <c r="H101" t="s">
-        <v>182</v>
+        <v>288</v>
       </c>
       <c r="K101">
         <v>52.66</v>
@@ -3434,13 +3752,13 @@
     </row>
     <row r="102" spans="6:15">
       <c r="F102" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="G102" t="s">
-        <v>178</v>
+        <v>284</v>
       </c>
       <c r="H102" t="s">
-        <v>182</v>
+        <v>288</v>
       </c>
       <c r="K102">
         <v>52.66</v>
@@ -3457,13 +3775,13 @@
     </row>
     <row r="103" spans="6:15">
       <c r="F103" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="G103" t="s">
-        <v>179</v>
+        <v>285</v>
       </c>
       <c r="H103" t="s">
-        <v>168</v>
+        <v>274</v>
       </c>
       <c r="K103">
         <v>833.34</v>
@@ -3480,13 +3798,13 @@
     </row>
     <row r="104" spans="6:15">
       <c r="F104" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="G104" t="s">
-        <v>169</v>
+        <v>275</v>
       </c>
       <c r="H104" t="s">
-        <v>196</v>
+        <v>302</v>
       </c>
       <c r="K104">
         <v>240.65</v>
@@ -3503,13 +3821,13 @@
     </row>
     <row r="105" spans="6:15">
       <c r="F105" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="G105" t="s">
-        <v>157</v>
+        <v>263</v>
       </c>
       <c r="H105" t="s">
-        <v>154</v>
+        <v>260</v>
       </c>
       <c r="K105">
         <v>746.63</v>
@@ -3526,13 +3844,13 @@
     </row>
     <row r="106" spans="6:15">
       <c r="F106" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G106" t="s">
-        <v>157</v>
+        <v>263</v>
       </c>
       <c r="H106" t="s">
-        <v>154</v>
+        <v>260</v>
       </c>
       <c r="K106">
         <v>736.63</v>
@@ -3549,13 +3867,13 @@
     </row>
     <row r="107" spans="6:15">
       <c r="F107" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="G107" t="s">
-        <v>178</v>
+        <v>284</v>
       </c>
       <c r="H107" t="s">
-        <v>182</v>
+        <v>288</v>
       </c>
       <c r="K107">
         <v>283.31</v>
@@ -3572,13 +3890,13 @@
     </row>
     <row r="108" spans="6:15">
       <c r="F108" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="G108" t="s">
-        <v>180</v>
+        <v>286</v>
       </c>
       <c r="H108" t="s">
-        <v>151</v>
+        <v>257</v>
       </c>
       <c r="K108">
         <v>309.3</v>
@@ -3595,13 +3913,13 @@
     </row>
     <row r="109" spans="6:15">
       <c r="F109" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G109" t="s">
-        <v>180</v>
+        <v>286</v>
       </c>
       <c r="H109" t="s">
-        <v>151</v>
+        <v>257</v>
       </c>
       <c r="K109">
         <v>160.65</v>
@@ -3618,13 +3936,13 @@
     </row>
     <row r="110" spans="6:15">
       <c r="F110" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="G110" t="s">
-        <v>145</v>
+        <v>251</v>
       </c>
       <c r="H110" t="s">
-        <v>223</v>
+        <v>329</v>
       </c>
       <c r="K110">
         <v>203.26</v>
@@ -3641,13 +3959,13 @@
     </row>
     <row r="111" spans="6:15">
       <c r="F111" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="G111" t="s">
-        <v>181</v>
+        <v>287</v>
       </c>
       <c r="H111" t="s">
-        <v>206</v>
+        <v>312</v>
       </c>
       <c r="K111">
         <v>483.92</v>
@@ -3664,13 +3982,13 @@
     </row>
     <row r="112" spans="6:15">
       <c r="F112" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="G112" t="s">
-        <v>181</v>
+        <v>287</v>
       </c>
       <c r="H112" t="s">
-        <v>206</v>
+        <v>312</v>
       </c>
       <c r="K112">
         <v>343.27</v>
@@ -3687,13 +4005,13 @@
     </row>
     <row r="113" spans="6:15">
       <c r="F113" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="G113" t="s">
-        <v>182</v>
+        <v>288</v>
       </c>
       <c r="H113" t="s">
-        <v>184</v>
+        <v>290</v>
       </c>
       <c r="K113">
         <v>0</v>
@@ -3710,13 +4028,13 @@
     </row>
     <row r="114" spans="6:15">
       <c r="F114" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="G114" t="s">
-        <v>183</v>
+        <v>289</v>
       </c>
       <c r="H114" t="s">
-        <v>186</v>
+        <v>292</v>
       </c>
       <c r="K114">
         <v>73.66</v>
@@ -3733,13 +4051,13 @@
     </row>
     <row r="115" spans="6:15">
       <c r="F115" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="G115" t="s">
-        <v>184</v>
+        <v>290</v>
       </c>
       <c r="H115" t="s">
-        <v>152</v>
+        <v>258</v>
       </c>
       <c r="K115">
         <v>510.99</v>
@@ -3756,13 +4074,13 @@
     </row>
     <row r="116" spans="6:15">
       <c r="F116" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G116" t="s">
-        <v>184</v>
+        <v>290</v>
       </c>
       <c r="H116" t="s">
-        <v>152</v>
+        <v>258</v>
       </c>
       <c r="K116">
         <v>562.66</v>
@@ -3779,13 +4097,13 @@
     </row>
     <row r="117" spans="6:15">
       <c r="F117" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="G117" t="s">
-        <v>168</v>
+        <v>274</v>
       </c>
       <c r="H117" t="s">
-        <v>168</v>
+        <v>274</v>
       </c>
       <c r="K117">
         <v>3603.36</v>
@@ -3802,13 +4120,13 @@
     </row>
     <row r="118" spans="6:15">
       <c r="F118" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="G118" t="s">
-        <v>185</v>
+        <v>291</v>
       </c>
       <c r="H118" t="s">
-        <v>187</v>
+        <v>293</v>
       </c>
       <c r="K118">
         <v>595.99</v>
@@ -3825,13 +4143,13 @@
     </row>
     <row r="119" spans="6:15">
       <c r="F119" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="G119" t="s">
-        <v>185</v>
+        <v>291</v>
       </c>
       <c r="H119" t="s">
-        <v>187</v>
+        <v>293</v>
       </c>
       <c r="K119">
         <v>401.33</v>
@@ -3848,13 +4166,13 @@
     </row>
     <row r="120" spans="6:15">
       <c r="F120" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="G120" t="s">
-        <v>185</v>
+        <v>291</v>
       </c>
       <c r="H120" t="s">
-        <v>187</v>
+        <v>293</v>
       </c>
       <c r="K120">
         <v>138.66</v>
@@ -3871,13 +4189,13 @@
     </row>
     <row r="121" spans="6:15">
       <c r="F121" t="s">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="G121" t="s">
-        <v>186</v>
+        <v>292</v>
       </c>
       <c r="H121" t="s">
-        <v>178</v>
+        <v>284</v>
       </c>
       <c r="K121">
         <v>30.66</v>
@@ -3897,10 +4215,10 @@
         <v>16</v>
       </c>
       <c r="G122" t="s">
-        <v>187</v>
+        <v>293</v>
       </c>
       <c r="H122" t="s">
-        <v>225</v>
+        <v>331</v>
       </c>
       <c r="K122">
         <v>187.99</v>
@@ -3920,10 +4238,10 @@
         <v>17</v>
       </c>
       <c r="G123" t="s">
-        <v>187</v>
+        <v>293</v>
       </c>
       <c r="H123" t="s">
-        <v>225</v>
+        <v>331</v>
       </c>
       <c r="K123">
         <v>77.33</v>
@@ -3940,13 +4258,13 @@
     </row>
     <row r="124" spans="6:15">
       <c r="F124" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="G124" t="s">
-        <v>188</v>
+        <v>294</v>
       </c>
       <c r="H124" t="s">
-        <v>181</v>
+        <v>287</v>
       </c>
       <c r="K124">
         <v>20.65</v>
@@ -3963,13 +4281,13 @@
     </row>
     <row r="125" spans="6:15">
       <c r="F125" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="G125" t="s">
-        <v>189</v>
+        <v>295</v>
       </c>
       <c r="H125" t="s">
-        <v>188</v>
+        <v>294</v>
       </c>
       <c r="K125">
         <v>578.65</v>
@@ -3986,13 +4304,13 @@
     </row>
     <row r="126" spans="6:15">
       <c r="F126" t="s">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="G126" t="s">
-        <v>190</v>
+        <v>296</v>
       </c>
       <c r="H126" t="s">
-        <v>199</v>
+        <v>305</v>
       </c>
       <c r="K126">
         <v>105.31</v>
@@ -4009,13 +4327,13 @@
     </row>
     <row r="127" spans="6:15">
       <c r="F127" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="G127" t="s">
-        <v>189</v>
+        <v>295</v>
       </c>
       <c r="H127" t="s">
-        <v>188</v>
+        <v>294</v>
       </c>
       <c r="K127">
         <v>338.65</v>
@@ -4032,13 +4350,13 @@
     </row>
     <row r="128" spans="6:15">
       <c r="F128" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="G128" t="s">
-        <v>189</v>
+        <v>295</v>
       </c>
       <c r="H128" t="s">
-        <v>188</v>
+        <v>294</v>
       </c>
       <c r="K128">
         <v>448.65</v>
@@ -4055,13 +4373,13 @@
     </row>
     <row r="129" spans="6:15">
       <c r="F129" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G129" t="s">
-        <v>189</v>
+        <v>295</v>
       </c>
       <c r="H129" t="s">
-        <v>188</v>
+        <v>294</v>
       </c>
       <c r="K129">
         <v>298.65</v>
@@ -4078,13 +4396,13 @@
     </row>
     <row r="130" spans="6:15">
       <c r="F130" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="G130" t="s">
-        <v>191</v>
+        <v>297</v>
       </c>
       <c r="H130" t="s">
-        <v>185</v>
+        <v>291</v>
       </c>
       <c r="K130">
         <v>143.31</v>
@@ -4101,13 +4419,13 @@
     </row>
     <row r="131" spans="6:15">
       <c r="F131" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="G131" t="s">
-        <v>170</v>
+        <v>276</v>
       </c>
       <c r="H131" t="s">
-        <v>188</v>
+        <v>294</v>
       </c>
       <c r="K131">
         <v>6.65</v>
@@ -4124,13 +4442,13 @@
     </row>
     <row r="132" spans="6:15">
       <c r="F132" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="G132" t="s">
-        <v>170</v>
+        <v>276</v>
       </c>
       <c r="H132" t="s">
-        <v>189</v>
+        <v>295</v>
       </c>
       <c r="K132">
         <v>128.65</v>
@@ -4147,13 +4465,13 @@
     </row>
     <row r="133" spans="6:15">
       <c r="F133" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="G133" t="s">
-        <v>160</v>
+        <v>266</v>
       </c>
       <c r="H133" t="s">
-        <v>192</v>
+        <v>298</v>
       </c>
       <c r="K133">
         <v>86.66</v>
@@ -4170,13 +4488,13 @@
     </row>
     <row r="134" spans="6:15">
       <c r="F134" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G134" t="s">
-        <v>160</v>
+        <v>266</v>
       </c>
       <c r="H134" t="s">
-        <v>192</v>
+        <v>298</v>
       </c>
       <c r="K134">
         <v>693.3099999999999</v>
@@ -4193,13 +4511,13 @@
     </row>
     <row r="135" spans="6:15">
       <c r="F135" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G135" t="s">
-        <v>160</v>
+        <v>266</v>
       </c>
       <c r="H135" t="s">
-        <v>192</v>
+        <v>298</v>
       </c>
       <c r="K135">
         <v>993.3099999999999</v>
@@ -4216,13 +4534,13 @@
     </row>
     <row r="136" spans="6:15">
       <c r="F136" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G136" t="s">
-        <v>160</v>
+        <v>266</v>
       </c>
       <c r="H136" t="s">
-        <v>192</v>
+        <v>298</v>
       </c>
       <c r="K136">
         <v>246.66</v>
@@ -4239,13 +4557,13 @@
     </row>
     <row r="137" spans="6:15">
       <c r="F137" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G137" t="s">
-        <v>192</v>
+        <v>298</v>
       </c>
       <c r="H137" t="s">
-        <v>193</v>
+        <v>299</v>
       </c>
       <c r="K137">
         <v>783.28</v>
@@ -4262,13 +4580,13 @@
     </row>
     <row r="138" spans="6:15">
       <c r="F138" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G138" t="s">
-        <v>168</v>
+        <v>274</v>
       </c>
       <c r="H138" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
       <c r="K138">
         <v>53.36</v>
@@ -4285,13 +4603,13 @@
     </row>
     <row r="139" spans="6:15">
       <c r="F139" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G139" t="s">
-        <v>168</v>
+        <v>274</v>
       </c>
       <c r="H139" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
       <c r="K139">
         <v>213.43</v>
@@ -4308,13 +4626,13 @@
     </row>
     <row r="140" spans="6:15">
       <c r="F140" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="G140" t="s">
-        <v>193</v>
+        <v>299</v>
       </c>
       <c r="H140" t="s">
-        <v>161</v>
+        <v>267</v>
       </c>
       <c r="K140">
         <v>1397.33</v>
@@ -4334,10 +4652,10 @@
         <v>21</v>
       </c>
       <c r="G141" t="s">
-        <v>193</v>
+        <v>299</v>
       </c>
       <c r="H141" t="s">
-        <v>161</v>
+        <v>267</v>
       </c>
       <c r="K141">
         <v>3353.31</v>
@@ -4357,10 +4675,10 @@
         <v>21</v>
       </c>
       <c r="G142" t="s">
-        <v>193</v>
+        <v>299</v>
       </c>
       <c r="H142" t="s">
-        <v>161</v>
+        <v>267</v>
       </c>
       <c r="K142">
         <v>1797.33</v>
@@ -4380,10 +4698,10 @@
         <v>21</v>
       </c>
       <c r="G143" t="s">
-        <v>193</v>
+        <v>299</v>
       </c>
       <c r="H143" t="s">
-        <v>161</v>
+        <v>267</v>
       </c>
       <c r="K143">
         <v>1597.33</v>
@@ -4403,10 +4721,10 @@
         <v>21</v>
       </c>
       <c r="G144" t="s">
-        <v>193</v>
+        <v>299</v>
       </c>
       <c r="H144" t="s">
-        <v>161</v>
+        <v>267</v>
       </c>
       <c r="K144">
         <v>948.66</v>
@@ -4423,13 +4741,13 @@
     </row>
     <row r="145" spans="6:15">
       <c r="F145" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G145" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
       <c r="H145" t="s">
-        <v>195</v>
+        <v>301</v>
       </c>
       <c r="K145">
         <v>2993.36</v>
@@ -4449,10 +4767,10 @@
         <v>21</v>
       </c>
       <c r="G146" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
       <c r="H146" t="s">
-        <v>195</v>
+        <v>301</v>
       </c>
       <c r="K146">
         <v>1117.34</v>
@@ -4472,10 +4790,10 @@
         <v>21</v>
       </c>
       <c r="G147" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
       <c r="H147" t="s">
-        <v>195</v>
+        <v>301</v>
       </c>
       <c r="K147">
         <v>279.34</v>
@@ -4495,10 +4813,10 @@
         <v>21</v>
       </c>
       <c r="G148" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
       <c r="H148" t="s">
-        <v>195</v>
+        <v>301</v>
       </c>
       <c r="K148">
         <v>2493.36</v>
@@ -4515,13 +4833,13 @@
     </row>
     <row r="149" spans="6:15">
       <c r="F149" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G149" t="s">
-        <v>195</v>
+        <v>301</v>
       </c>
       <c r="H149" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="K149">
         <v>906.72</v>
@@ -4538,13 +4856,13 @@
     </row>
     <row r="150" spans="6:15">
       <c r="F150" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G150" t="s">
-        <v>167</v>
+        <v>273</v>
       </c>
       <c r="H150" t="s">
-        <v>179</v>
+        <v>285</v>
       </c>
       <c r="K150">
         <v>358.01</v>
@@ -4561,13 +4879,13 @@
     </row>
     <row r="151" spans="6:15">
       <c r="F151" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G151" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
       <c r="H151" t="s">
-        <v>195</v>
+        <v>301</v>
       </c>
       <c r="K151">
         <v>993.36</v>
@@ -4587,10 +4905,10 @@
         <v>21</v>
       </c>
       <c r="G152" t="s">
-        <v>195</v>
+        <v>301</v>
       </c>
       <c r="H152" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="K152">
         <v>503.36</v>
@@ -4607,13 +4925,13 @@
     </row>
     <row r="153" spans="6:15">
       <c r="F153" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G153" t="s">
-        <v>167</v>
+        <v>273</v>
       </c>
       <c r="H153" t="s">
-        <v>179</v>
+        <v>285</v>
       </c>
       <c r="K153">
         <v>2786.72</v>
@@ -4630,13 +4948,13 @@
     </row>
     <row r="154" spans="6:15">
       <c r="F154" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G154" t="s">
-        <v>168</v>
+        <v>274</v>
       </c>
       <c r="H154" t="s">
-        <v>168</v>
+        <v>274</v>
       </c>
       <c r="K154">
         <v>1893.36</v>
@@ -4653,13 +4971,13 @@
     </row>
     <row r="155" spans="6:15">
       <c r="F155" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="G155" t="s">
-        <v>188</v>
+        <v>294</v>
       </c>
       <c r="H155" t="s">
-        <v>181</v>
+        <v>287</v>
       </c>
       <c r="K155">
         <v>18.65</v>
@@ -4676,13 +4994,13 @@
     </row>
     <row r="156" spans="6:15">
       <c r="F156" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="G156" t="s">
-        <v>168</v>
+        <v>274</v>
       </c>
       <c r="H156" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
       <c r="K156">
         <v>1491.68</v>
@@ -4699,13 +5017,13 @@
     </row>
     <row r="157" spans="6:15">
       <c r="F157" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="G157" t="s">
-        <v>168</v>
+        <v>274</v>
       </c>
       <c r="H157" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
       <c r="K157">
         <v>1296.68</v>
@@ -4722,13 +5040,13 @@
     </row>
     <row r="158" spans="6:15">
       <c r="F158" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="G158" t="s">
-        <v>167</v>
+        <v>273</v>
       </c>
       <c r="H158" t="s">
-        <v>179</v>
+        <v>285</v>
       </c>
       <c r="K158">
         <v>1978.68</v>
@@ -4745,13 +5063,13 @@
     </row>
     <row r="159" spans="6:15">
       <c r="F159" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G159" t="s">
-        <v>179</v>
+        <v>285</v>
       </c>
       <c r="H159" t="s">
-        <v>168</v>
+        <v>274</v>
       </c>
       <c r="K159">
         <v>1393.36</v>
@@ -4768,13 +5086,13 @@
     </row>
     <row r="160" spans="6:15">
       <c r="F160" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="G160" t="s">
-        <v>168</v>
+        <v>274</v>
       </c>
       <c r="H160" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
       <c r="K160">
         <v>1661.68</v>
@@ -4791,13 +5109,13 @@
     </row>
     <row r="161" spans="6:15">
       <c r="F161" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="G161" t="s">
-        <v>168</v>
+        <v>274</v>
       </c>
       <c r="H161" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
       <c r="K161">
         <v>961.6799999999999</v>
@@ -4814,13 +5132,13 @@
     </row>
     <row r="162" spans="6:15">
       <c r="F162" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="G162" t="s">
-        <v>195</v>
+        <v>301</v>
       </c>
       <c r="H162" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="K162">
         <v>245.04</v>
@@ -4837,13 +5155,13 @@
     </row>
     <row r="163" spans="6:15">
       <c r="F163" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="G163" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="H163" t="s">
-        <v>159</v>
+        <v>265</v>
       </c>
       <c r="K163">
         <v>586.63</v>
@@ -4860,13 +5178,13 @@
     </row>
     <row r="164" spans="6:15">
       <c r="F164" t="s">
-        <v>28</v>
+        <v>102</v>
       </c>
       <c r="G164" t="s">
-        <v>186</v>
+        <v>292</v>
       </c>
       <c r="H164" t="s">
-        <v>178</v>
+        <v>284</v>
       </c>
       <c r="K164">
         <v>207.99</v>
@@ -4883,13 +5201,13 @@
     </row>
     <row r="165" spans="6:15">
       <c r="F165" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G165" t="s">
-        <v>186</v>
+        <v>292</v>
       </c>
       <c r="H165" t="s">
-        <v>178</v>
+        <v>284</v>
       </c>
       <c r="K165">
         <v>178.66</v>
@@ -4906,13 +5224,13 @@
     </row>
     <row r="166" spans="6:15">
       <c r="F166" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G166" t="s">
-        <v>186</v>
+        <v>292</v>
       </c>
       <c r="H166" t="s">
-        <v>178</v>
+        <v>284</v>
       </c>
       <c r="K166">
         <v>296.66</v>
@@ -4929,13 +5247,13 @@
     </row>
     <row r="167" spans="6:15">
       <c r="F167" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="G167" t="s">
-        <v>189</v>
+        <v>295</v>
       </c>
       <c r="H167" t="s">
-        <v>188</v>
+        <v>294</v>
       </c>
       <c r="K167">
         <v>66.53</v>
@@ -4952,13 +5270,13 @@
     </row>
     <row r="168" spans="6:15">
       <c r="F168" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="G168" t="s">
-        <v>188</v>
+        <v>294</v>
       </c>
       <c r="H168" t="s">
-        <v>181</v>
+        <v>287</v>
       </c>
       <c r="K168">
         <v>25.31</v>
@@ -4975,13 +5293,13 @@
     </row>
     <row r="169" spans="6:15">
       <c r="F169" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="G169" t="s">
-        <v>196</v>
+        <v>302</v>
       </c>
       <c r="H169" t="s">
-        <v>233</v>
+        <v>339</v>
       </c>
       <c r="K169">
         <v>110.65</v>
@@ -4998,13 +5316,13 @@
     </row>
     <row r="170" spans="6:15">
       <c r="F170" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="G170" t="s">
-        <v>197</v>
+        <v>303</v>
       </c>
       <c r="H170" t="s">
-        <v>201</v>
+        <v>307</v>
       </c>
       <c r="K170">
         <v>1197.99</v>
@@ -5021,13 +5339,13 @@
     </row>
     <row r="171" spans="6:15">
       <c r="F171" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="G171" t="s">
-        <v>197</v>
+        <v>303</v>
       </c>
       <c r="H171" t="s">
-        <v>201</v>
+        <v>307</v>
       </c>
       <c r="K171">
         <v>219.33</v>
@@ -5044,13 +5362,13 @@
     </row>
     <row r="172" spans="6:15">
       <c r="F172" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="G172" t="s">
-        <v>197</v>
+        <v>303</v>
       </c>
       <c r="H172" t="s">
-        <v>201</v>
+        <v>307</v>
       </c>
       <c r="K172">
         <v>548.66</v>
@@ -5067,13 +5385,13 @@
     </row>
     <row r="173" spans="6:15">
       <c r="F173" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="G173" t="s">
-        <v>198</v>
+        <v>304</v>
       </c>
       <c r="H173" t="s">
-        <v>222</v>
+        <v>328</v>
       </c>
       <c r="K173">
         <v>325.3</v>
@@ -5090,13 +5408,13 @@
     </row>
     <row r="174" spans="6:15">
       <c r="F174" t="s">
-        <v>45</v>
+        <v>108</v>
       </c>
       <c r="G174" t="s">
-        <v>199</v>
+        <v>305</v>
       </c>
       <c r="H174" t="s">
-        <v>170</v>
+        <v>276</v>
       </c>
       <c r="K174">
         <v>905.3099999999999</v>
@@ -5113,13 +5431,13 @@
     </row>
     <row r="175" spans="6:15">
       <c r="F175" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="G175" t="s">
-        <v>199</v>
+        <v>305</v>
       </c>
       <c r="H175" t="s">
-        <v>170</v>
+        <v>276</v>
       </c>
       <c r="K175">
         <v>981.98</v>
@@ -5136,13 +5454,13 @@
     </row>
     <row r="176" spans="6:15">
       <c r="F176" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="G176" t="s">
-        <v>188</v>
+        <v>294</v>
       </c>
       <c r="H176" t="s">
-        <v>181</v>
+        <v>287</v>
       </c>
       <c r="K176">
         <v>10.65</v>
@@ -5159,13 +5477,13 @@
     </row>
     <row r="177" spans="6:15">
       <c r="F177" t="s">
-        <v>45</v>
+        <v>108</v>
       </c>
       <c r="G177" t="s">
-        <v>195</v>
+        <v>301</v>
       </c>
       <c r="H177" t="s">
-        <v>195</v>
+        <v>301</v>
       </c>
       <c r="K177">
         <v>1267.36</v>
@@ -5182,13 +5500,13 @@
     </row>
     <row r="178" spans="6:15">
       <c r="F178" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G178" t="s">
-        <v>195</v>
+        <v>301</v>
       </c>
       <c r="H178" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="K178">
         <v>153.36</v>
@@ -5205,13 +5523,13 @@
     </row>
     <row r="179" spans="6:15">
       <c r="F179" t="s">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="G179" t="s">
-        <v>159</v>
+        <v>265</v>
       </c>
       <c r="H179" t="s">
-        <v>160</v>
+        <v>266</v>
       </c>
       <c r="K179">
         <v>1697.33</v>
@@ -5228,13 +5546,13 @@
     </row>
     <row r="180" spans="6:15">
       <c r="F180" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G180" t="s">
-        <v>159</v>
+        <v>265</v>
       </c>
       <c r="H180" t="s">
-        <v>160</v>
+        <v>266</v>
       </c>
       <c r="K180">
         <v>1292.66</v>
@@ -5251,13 +5569,13 @@
     </row>
     <row r="181" spans="6:15">
       <c r="F181" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G181" t="s">
-        <v>159</v>
+        <v>265</v>
       </c>
       <c r="H181" t="s">
-        <v>160</v>
+        <v>266</v>
       </c>
       <c r="K181">
         <v>475.33</v>
@@ -5274,13 +5592,13 @@
     </row>
     <row r="182" spans="6:15">
       <c r="F182" t="s">
-        <v>50</v>
+        <v>111</v>
       </c>
       <c r="G182" t="s">
-        <v>200</v>
+        <v>306</v>
       </c>
       <c r="H182" t="s">
-        <v>156</v>
+        <v>262</v>
       </c>
       <c r="K182">
         <v>156.65</v>
@@ -5297,13 +5615,13 @@
     </row>
     <row r="183" spans="6:15">
       <c r="F183" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="G183" t="s">
-        <v>177</v>
+        <v>283</v>
       </c>
       <c r="H183" t="s">
-        <v>207</v>
+        <v>313</v>
       </c>
       <c r="K183">
         <v>88.65000000000001</v>
@@ -5320,13 +5638,13 @@
     </row>
     <row r="184" spans="6:15">
       <c r="F184" t="s">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="G184" t="s">
-        <v>201</v>
+        <v>307</v>
       </c>
       <c r="H184" t="s">
-        <v>186</v>
+        <v>292</v>
       </c>
       <c r="K184">
         <v>62.33</v>
@@ -5343,13 +5661,13 @@
     </row>
     <row r="185" spans="6:15">
       <c r="F185" t="s">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="G185" t="s">
-        <v>196</v>
+        <v>302</v>
       </c>
       <c r="H185" t="s">
-        <v>217</v>
+        <v>323</v>
       </c>
       <c r="K185">
         <v>102.65</v>
@@ -5366,13 +5684,13 @@
     </row>
     <row r="186" spans="6:15">
       <c r="F186" t="s">
-        <v>30</v>
+        <v>114</v>
       </c>
       <c r="G186" t="s">
-        <v>170</v>
+        <v>276</v>
       </c>
       <c r="H186" t="s">
-        <v>189</v>
+        <v>295</v>
       </c>
       <c r="K186">
         <v>297.98</v>
@@ -5389,13 +5707,13 @@
     </row>
     <row r="187" spans="6:15">
       <c r="F187" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G187" t="s">
-        <v>170</v>
+        <v>276</v>
       </c>
       <c r="H187" t="s">
-        <v>189</v>
+        <v>295</v>
       </c>
       <c r="K187">
         <v>198.65</v>
@@ -5412,13 +5730,13 @@
     </row>
     <row r="188" spans="6:15">
       <c r="F188" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="G188" t="s">
-        <v>167</v>
+        <v>273</v>
       </c>
       <c r="H188" t="s">
-        <v>168</v>
+        <v>274</v>
       </c>
       <c r="K188">
         <v>1073.36</v>
@@ -5435,13 +5753,13 @@
     </row>
     <row r="189" spans="6:15">
       <c r="F189" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="G189" t="s">
-        <v>167</v>
+        <v>273</v>
       </c>
       <c r="H189" t="s">
-        <v>168</v>
+        <v>274</v>
       </c>
       <c r="K189">
         <v>1186.72</v>
@@ -5458,13 +5776,13 @@
     </row>
     <row r="190" spans="6:15">
       <c r="F190" t="s">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="G190" t="s">
-        <v>179</v>
+        <v>285</v>
       </c>
       <c r="H190" t="s">
-        <v>168</v>
+        <v>274</v>
       </c>
       <c r="K190">
         <v>1446.72</v>
@@ -5484,10 +5802,10 @@
         <v>21</v>
       </c>
       <c r="G191" t="s">
-        <v>179</v>
+        <v>285</v>
       </c>
       <c r="H191" t="s">
-        <v>168</v>
+        <v>274</v>
       </c>
       <c r="K191">
         <v>2530.08</v>
@@ -5504,13 +5822,13 @@
     </row>
     <row r="192" spans="6:15">
       <c r="F192" t="s">
-        <v>32</v>
+        <v>118</v>
       </c>
       <c r="G192" t="s">
-        <v>175</v>
+        <v>281</v>
       </c>
       <c r="H192" t="s">
-        <v>226</v>
+        <v>332</v>
       </c>
       <c r="K192">
         <v>168.66</v>
@@ -5530,10 +5848,10 @@
         <v>21</v>
       </c>
       <c r="G193" t="s">
-        <v>175</v>
+        <v>281</v>
       </c>
       <c r="H193" t="s">
-        <v>226</v>
+        <v>332</v>
       </c>
       <c r="K193">
         <v>117.99</v>
@@ -5550,13 +5868,13 @@
     </row>
     <row r="194" spans="6:15">
       <c r="F194" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="G194" t="s">
-        <v>202</v>
+        <v>308</v>
       </c>
       <c r="H194" t="s">
-        <v>218</v>
+        <v>324</v>
       </c>
       <c r="K194">
         <v>1250.66</v>
@@ -5573,13 +5891,13 @@
     </row>
     <row r="195" spans="6:15">
       <c r="F195" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="G195" t="s">
-        <v>202</v>
+        <v>308</v>
       </c>
       <c r="H195" t="s">
-        <v>218</v>
+        <v>324</v>
       </c>
       <c r="K195">
         <v>549.33</v>
@@ -5596,13 +5914,13 @@
     </row>
     <row r="196" spans="6:15">
       <c r="F196" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="G196" t="s">
-        <v>202</v>
+        <v>308</v>
       </c>
       <c r="H196" t="s">
-        <v>218</v>
+        <v>324</v>
       </c>
       <c r="K196">
         <v>716.33</v>
@@ -5619,13 +5937,13 @@
     </row>
     <row r="197" spans="6:15">
       <c r="F197" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="G197" t="s">
-        <v>202</v>
+        <v>308</v>
       </c>
       <c r="H197" t="s">
-        <v>218</v>
+        <v>324</v>
       </c>
       <c r="K197">
         <v>839.33</v>
@@ -5642,13 +5960,13 @@
     </row>
     <row r="198" spans="6:15">
       <c r="F198" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="G198" t="s">
-        <v>202</v>
+        <v>308</v>
       </c>
       <c r="H198" t="s">
-        <v>218</v>
+        <v>324</v>
       </c>
       <c r="K198">
         <v>725.33</v>
@@ -5665,13 +5983,13 @@
     </row>
     <row r="199" spans="6:15">
       <c r="F199" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="G199" t="s">
-        <v>202</v>
+        <v>308</v>
       </c>
       <c r="H199" t="s">
-        <v>218</v>
+        <v>324</v>
       </c>
       <c r="K199">
         <v>709.33</v>
@@ -5688,13 +6006,13 @@
     </row>
     <row r="200" spans="6:15">
       <c r="F200" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="G200" t="s">
-        <v>202</v>
+        <v>308</v>
       </c>
       <c r="H200" t="s">
-        <v>218</v>
+        <v>324</v>
       </c>
       <c r="K200">
         <v>991.33</v>
@@ -5711,13 +6029,13 @@
     </row>
     <row r="201" spans="6:15">
       <c r="F201" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="G201" t="s">
-        <v>175</v>
+        <v>281</v>
       </c>
       <c r="H201" t="s">
-        <v>226</v>
+        <v>332</v>
       </c>
       <c r="K201">
         <v>286.66</v>
@@ -5734,13 +6052,13 @@
     </row>
     <row r="202" spans="6:15">
       <c r="F202" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="G202" t="s">
-        <v>202</v>
+        <v>308</v>
       </c>
       <c r="H202" t="s">
-        <v>218</v>
+        <v>324</v>
       </c>
       <c r="K202">
         <v>433.33</v>
@@ -5757,13 +6075,13 @@
     </row>
     <row r="203" spans="6:15">
       <c r="F203" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G203" t="s">
-        <v>202</v>
+        <v>308</v>
       </c>
       <c r="H203" t="s">
-        <v>218</v>
+        <v>324</v>
       </c>
       <c r="K203">
         <v>375.33</v>
@@ -5780,13 +6098,13 @@
     </row>
     <row r="204" spans="6:15">
       <c r="F204" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G204" t="s">
-        <v>202</v>
+        <v>308</v>
       </c>
       <c r="H204" t="s">
-        <v>218</v>
+        <v>324</v>
       </c>
       <c r="K204">
         <v>387.33</v>
@@ -5803,13 +6121,13 @@
     </row>
     <row r="205" spans="6:15">
       <c r="F205" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G205" t="s">
-        <v>202</v>
+        <v>308</v>
       </c>
       <c r="H205" t="s">
-        <v>218</v>
+        <v>324</v>
       </c>
       <c r="K205">
         <v>1390.66</v>
@@ -5826,13 +6144,13 @@
     </row>
     <row r="206" spans="6:15">
       <c r="F206" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G206" t="s">
-        <v>202</v>
+        <v>308</v>
       </c>
       <c r="H206" t="s">
-        <v>218</v>
+        <v>324</v>
       </c>
       <c r="K206">
         <v>516.33</v>
@@ -5849,13 +6167,13 @@
     </row>
     <row r="207" spans="6:15">
       <c r="F207" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G207" t="s">
-        <v>202</v>
+        <v>308</v>
       </c>
       <c r="H207" t="s">
-        <v>218</v>
+        <v>324</v>
       </c>
       <c r="K207">
         <v>770.33</v>
@@ -5872,13 +6190,13 @@
     </row>
     <row r="208" spans="6:15">
       <c r="F208" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="G208" t="s">
-        <v>202</v>
+        <v>308</v>
       </c>
       <c r="H208" t="s">
-        <v>218</v>
+        <v>324</v>
       </c>
       <c r="K208">
         <v>468.33</v>
@@ -5895,13 +6213,13 @@
     </row>
     <row r="209" spans="6:15">
       <c r="F209" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
       <c r="G209" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="H209" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="K209">
         <v>251.66</v>
@@ -5918,13 +6236,13 @@
     </row>
     <row r="210" spans="6:15">
       <c r="F210" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="G210" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="H210" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="K210">
         <v>470.66</v>
@@ -5941,13 +6259,13 @@
     </row>
     <row r="211" spans="6:15">
       <c r="F211" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="G211" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="H211" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="K211">
         <v>264.66</v>
@@ -5964,13 +6282,13 @@
     </row>
     <row r="212" spans="6:15">
       <c r="F212" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
       <c r="G212" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="H212" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="K212">
         <v>248.66</v>
@@ -5987,13 +6305,13 @@
     </row>
     <row r="213" spans="6:15">
       <c r="F213" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="G213" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="H213" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="K213">
         <v>131.33</v>
@@ -6010,13 +6328,13 @@
     </row>
     <row r="214" spans="6:15">
       <c r="F214" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="G214" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="H214" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="K214">
         <v>238.66</v>
@@ -6033,13 +6351,13 @@
     </row>
     <row r="215" spans="6:15">
       <c r="F215" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G215" t="s">
-        <v>205</v>
+        <v>311</v>
       </c>
       <c r="H215" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="K215">
         <v>160.66</v>
@@ -6056,13 +6374,13 @@
     </row>
     <row r="216" spans="6:15">
       <c r="F216" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G216" t="s">
-        <v>205</v>
+        <v>311</v>
       </c>
       <c r="H216" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="K216">
         <v>246.99</v>
@@ -6079,13 +6397,13 @@
     </row>
     <row r="217" spans="6:15">
       <c r="F217" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="G217" t="s">
-        <v>172</v>
+        <v>278</v>
       </c>
       <c r="H217" t="s">
-        <v>153</v>
+        <v>259</v>
       </c>
       <c r="K217">
         <v>18.65</v>
@@ -6102,13 +6420,13 @@
     </row>
     <row r="218" spans="6:15">
       <c r="F218" t="s">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="G218" t="s">
-        <v>172</v>
+        <v>278</v>
       </c>
       <c r="H218" t="s">
-        <v>153</v>
+        <v>259</v>
       </c>
       <c r="K218">
         <v>1062.33</v>
@@ -6125,13 +6443,13 @@
     </row>
     <row r="219" spans="6:15">
       <c r="F219" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="G219" t="s">
-        <v>172</v>
+        <v>278</v>
       </c>
       <c r="H219" t="s">
-        <v>153</v>
+        <v>259</v>
       </c>
       <c r="K219">
         <v>849.33</v>
@@ -6148,13 +6466,13 @@
     </row>
     <row r="220" spans="6:15">
       <c r="F220" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="G220" t="s">
-        <v>206</v>
+        <v>312</v>
       </c>
       <c r="H220" t="s">
-        <v>177</v>
+        <v>283</v>
       </c>
       <c r="K220">
         <v>375.98</v>
@@ -6171,13 +6489,13 @@
     </row>
     <row r="221" spans="6:15">
       <c r="F221" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="G221" t="s">
-        <v>156</v>
+        <v>262</v>
       </c>
       <c r="H221" t="s">
-        <v>174</v>
+        <v>280</v>
       </c>
       <c r="K221">
         <v>226.63</v>
@@ -6194,13 +6512,13 @@
     </row>
     <row r="222" spans="6:15">
       <c r="F222" t="s">
-        <v>65</v>
+        <v>123</v>
       </c>
       <c r="G222" t="s">
-        <v>207</v>
+        <v>313</v>
       </c>
       <c r="H222" t="s">
-        <v>166</v>
+        <v>272</v>
       </c>
       <c r="K222">
         <v>139.13</v>
@@ -6217,13 +6535,13 @@
     </row>
     <row r="223" spans="6:15">
       <c r="F223" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="G223" t="s">
-        <v>207</v>
+        <v>313</v>
       </c>
       <c r="H223" t="s">
-        <v>166</v>
+        <v>272</v>
       </c>
       <c r="K223">
         <v>83.48</v>
@@ -6240,13 +6558,13 @@
     </row>
     <row r="224" spans="6:15">
       <c r="F224" t="s">
-        <v>32</v>
+        <v>124</v>
       </c>
       <c r="G224" t="s">
-        <v>208</v>
+        <v>314</v>
       </c>
       <c r="H224" t="s">
-        <v>210</v>
+        <v>316</v>
       </c>
       <c r="K224">
         <v>493.36</v>
@@ -6266,10 +6584,10 @@
         <v>21</v>
       </c>
       <c r="G225" t="s">
-        <v>208</v>
+        <v>314</v>
       </c>
       <c r="H225" t="s">
-        <v>210</v>
+        <v>316</v>
       </c>
       <c r="K225">
         <v>502.01</v>
@@ -6286,13 +6604,13 @@
     </row>
     <row r="226" spans="6:15">
       <c r="F226" t="s">
-        <v>32</v>
+        <v>118</v>
       </c>
       <c r="G226" t="s">
-        <v>209</v>
+        <v>315</v>
       </c>
       <c r="H226" t="s">
-        <v>216</v>
+        <v>322</v>
       </c>
       <c r="K226">
         <v>611.6799999999999</v>
@@ -6312,10 +6630,10 @@
         <v>21</v>
       </c>
       <c r="G227" t="s">
-        <v>209</v>
+        <v>315</v>
       </c>
       <c r="H227" t="s">
-        <v>216</v>
+        <v>322</v>
       </c>
       <c r="K227">
         <v>581.6799999999999</v>
@@ -6332,13 +6650,13 @@
     </row>
     <row r="228" spans="6:15">
       <c r="F228" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G228" t="s">
-        <v>210</v>
+        <v>316</v>
       </c>
       <c r="H228" t="s">
-        <v>230</v>
+        <v>336</v>
       </c>
       <c r="K228">
         <v>804.02</v>
@@ -6355,13 +6673,13 @@
     </row>
     <row r="229" spans="6:15">
       <c r="F229" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="G229" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="H229" t="s">
-        <v>209</v>
+        <v>315</v>
       </c>
       <c r="K229">
         <v>576.6799999999999</v>
@@ -6378,13 +6696,13 @@
     </row>
     <row r="230" spans="6:15">
       <c r="F230" t="s">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="G230" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="H230" t="s">
-        <v>209</v>
+        <v>315</v>
       </c>
       <c r="K230">
         <v>1730.04</v>
@@ -6401,13 +6719,13 @@
     </row>
     <row r="231" spans="6:15">
       <c r="F231" t="s">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="G231" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="H231" t="s">
-        <v>209</v>
+        <v>315</v>
       </c>
       <c r="K231">
         <v>1021.68</v>
@@ -6424,13 +6742,13 @@
     </row>
     <row r="232" spans="6:15">
       <c r="F232" t="s">
-        <v>83</v>
+        <v>127</v>
       </c>
       <c r="G232" t="s">
-        <v>209</v>
+        <v>315</v>
       </c>
       <c r="H232" t="s">
-        <v>216</v>
+        <v>322</v>
       </c>
       <c r="K232">
         <v>611.6799999999999</v>
@@ -6447,13 +6765,13 @@
     </row>
     <row r="233" spans="6:15">
       <c r="F233" t="s">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="G233" t="s">
-        <v>209</v>
+        <v>315</v>
       </c>
       <c r="H233" t="s">
-        <v>216</v>
+        <v>322</v>
       </c>
       <c r="K233">
         <v>730.35</v>
@@ -6470,13 +6788,13 @@
     </row>
     <row r="234" spans="6:15">
       <c r="F234" t="s">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="G234" t="s">
-        <v>209</v>
+        <v>315</v>
       </c>
       <c r="H234" t="s">
-        <v>216</v>
+        <v>322</v>
       </c>
       <c r="K234">
         <v>1103.36</v>
@@ -6493,13 +6811,13 @@
     </row>
     <row r="235" spans="6:15">
       <c r="F235" t="s">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="G235" t="s">
-        <v>168</v>
+        <v>274</v>
       </c>
       <c r="H235" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
       <c r="K235">
         <v>296.68</v>
@@ -6516,13 +6834,13 @@
     </row>
     <row r="236" spans="6:15">
       <c r="F236" t="s">
-        <v>48</v>
+        <v>129</v>
       </c>
       <c r="G236" t="s">
-        <v>186</v>
+        <v>292</v>
       </c>
       <c r="H236" t="s">
-        <v>178</v>
+        <v>284</v>
       </c>
       <c r="K236">
         <v>42.67</v>
@@ -6539,13 +6857,13 @@
     </row>
     <row r="237" spans="6:15">
       <c r="F237" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G237" t="s">
-        <v>186</v>
+        <v>292</v>
       </c>
       <c r="H237" t="s">
-        <v>178</v>
+        <v>284</v>
       </c>
       <c r="K237">
         <v>60.99</v>
@@ -6562,13 +6880,13 @@
     </row>
     <row r="238" spans="6:15">
       <c r="F238" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G238" t="s">
-        <v>211</v>
+        <v>317</v>
       </c>
       <c r="H238" t="s">
-        <v>178</v>
+        <v>284</v>
       </c>
       <c r="K238">
         <v>42.66</v>
@@ -6585,13 +6903,13 @@
     </row>
     <row r="239" spans="6:15">
       <c r="F239" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G239" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="H239" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="K239">
         <v>1293.25</v>
@@ -6608,13 +6926,13 @@
     </row>
     <row r="240" spans="6:15">
       <c r="F240" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="G240" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="H240" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="K240">
         <v>323.31</v>
@@ -6631,13 +6949,13 @@
     </row>
     <row r="241" spans="6:15">
       <c r="F241" t="s">
-        <v>23</v>
+        <v>130</v>
       </c>
       <c r="G241" t="s">
-        <v>176</v>
+        <v>282</v>
       </c>
       <c r="H241" t="s">
-        <v>159</v>
+        <v>265</v>
       </c>
       <c r="K241">
         <v>433.31</v>
@@ -6654,13 +6972,13 @@
     </row>
     <row r="242" spans="6:15">
       <c r="F242" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G242" t="s">
-        <v>159</v>
+        <v>265</v>
       </c>
       <c r="H242" t="s">
-        <v>160</v>
+        <v>266</v>
       </c>
       <c r="K242">
         <v>216.33</v>
@@ -6677,13 +6995,13 @@
     </row>
     <row r="243" spans="6:15">
       <c r="F243" t="s">
-        <v>43</v>
+        <v>131</v>
       </c>
       <c r="G243" t="s">
-        <v>213</v>
+        <v>319</v>
       </c>
       <c r="H243" t="s">
-        <v>214</v>
+        <v>320</v>
       </c>
       <c r="K243">
         <v>216.68</v>
@@ -6700,13 +7018,13 @@
     </row>
     <row r="244" spans="6:15">
       <c r="F244" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="G244" t="s">
-        <v>214</v>
+        <v>320</v>
       </c>
       <c r="H244" t="s">
-        <v>147</v>
+        <v>253</v>
       </c>
       <c r="K244">
         <v>233.36</v>
@@ -6723,13 +7041,13 @@
     </row>
     <row r="245" spans="6:15">
       <c r="F245" t="s">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="G245" t="s">
-        <v>211</v>
+        <v>317</v>
       </c>
       <c r="H245" t="s">
-        <v>178</v>
+        <v>284</v>
       </c>
       <c r="K245">
         <v>438.66</v>
@@ -6746,13 +7064,13 @@
     </row>
     <row r="246" spans="6:15">
       <c r="F246" t="s">
-        <v>87</v>
+        <v>133</v>
       </c>
       <c r="G246" t="s">
-        <v>211</v>
+        <v>317</v>
       </c>
       <c r="H246" t="s">
-        <v>178</v>
+        <v>284</v>
       </c>
       <c r="K246">
         <v>269.33</v>
@@ -6769,13 +7087,13 @@
     </row>
     <row r="247" spans="6:15">
       <c r="F247" t="s">
-        <v>88</v>
+        <v>134</v>
       </c>
       <c r="G247" t="s">
-        <v>215</v>
+        <v>321</v>
       </c>
       <c r="H247" t="s">
-        <v>217</v>
+        <v>323</v>
       </c>
       <c r="K247">
         <v>292.65</v>
@@ -6792,13 +7110,13 @@
     </row>
     <row r="248" spans="6:15">
       <c r="F248" t="s">
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="G248" t="s">
-        <v>150</v>
+        <v>256</v>
       </c>
       <c r="H248" t="s">
-        <v>198</v>
+        <v>304</v>
       </c>
       <c r="K248">
         <v>102.26</v>
@@ -6815,13 +7133,13 @@
     </row>
     <row r="249" spans="6:15">
       <c r="F249" t="s">
-        <v>89</v>
+        <v>136</v>
       </c>
       <c r="G249" t="s">
-        <v>201</v>
+        <v>307</v>
       </c>
       <c r="H249" t="s">
-        <v>186</v>
+        <v>292</v>
       </c>
       <c r="K249">
         <v>911.66</v>
@@ -6838,13 +7156,13 @@
     </row>
     <row r="250" spans="6:15">
       <c r="F250" t="s">
-        <v>90</v>
+        <v>137</v>
       </c>
       <c r="G250" t="s">
-        <v>201</v>
+        <v>307</v>
       </c>
       <c r="H250" t="s">
-        <v>186</v>
+        <v>292</v>
       </c>
       <c r="K250">
         <v>1026.66</v>
@@ -6861,13 +7179,13 @@
     </row>
     <row r="251" spans="6:15">
       <c r="F251" t="s">
-        <v>91</v>
+        <v>138</v>
       </c>
       <c r="G251" t="s">
-        <v>152</v>
+        <v>258</v>
       </c>
       <c r="H251" t="s">
-        <v>191</v>
+        <v>297</v>
       </c>
       <c r="K251">
         <v>221.33</v>
@@ -6884,13 +7202,13 @@
     </row>
     <row r="252" spans="6:15">
       <c r="F252" t="s">
-        <v>92</v>
+        <v>139</v>
       </c>
       <c r="G252" t="s">
-        <v>152</v>
+        <v>258</v>
       </c>
       <c r="H252" t="s">
-        <v>191</v>
+        <v>297</v>
       </c>
       <c r="K252">
         <v>174.33</v>
@@ -6907,13 +7225,13 @@
     </row>
     <row r="253" spans="6:15">
       <c r="F253" t="s">
-        <v>92</v>
+        <v>139</v>
       </c>
       <c r="G253" t="s">
-        <v>152</v>
+        <v>258</v>
       </c>
       <c r="H253" t="s">
-        <v>191</v>
+        <v>297</v>
       </c>
       <c r="K253">
         <v>282.99</v>
@@ -6930,13 +7248,13 @@
     </row>
     <row r="254" spans="6:15">
       <c r="F254" t="s">
-        <v>93</v>
+        <v>140</v>
       </c>
       <c r="G254" t="s">
-        <v>191</v>
+        <v>297</v>
       </c>
       <c r="H254" t="s">
-        <v>185</v>
+        <v>291</v>
       </c>
       <c r="K254">
         <v>353.31</v>
@@ -6953,13 +7271,13 @@
     </row>
     <row r="255" spans="6:15">
       <c r="F255" t="s">
-        <v>94</v>
+        <v>141</v>
       </c>
       <c r="G255" t="s">
-        <v>143</v>
+        <v>249</v>
       </c>
       <c r="H255" t="s">
-        <v>180</v>
+        <v>286</v>
       </c>
       <c r="K255">
         <v>214.56</v>
@@ -6976,13 +7294,13 @@
     </row>
     <row r="256" spans="6:15">
       <c r="F256" t="s">
-        <v>95</v>
+        <v>142</v>
       </c>
       <c r="G256" t="s">
-        <v>143</v>
+        <v>249</v>
       </c>
       <c r="H256" t="s">
-        <v>180</v>
+        <v>286</v>
       </c>
       <c r="K256">
         <v>15.33</v>
@@ -6999,13 +7317,13 @@
     </row>
     <row r="257" spans="6:15">
       <c r="F257" t="s">
-        <v>96</v>
+        <v>143</v>
       </c>
       <c r="G257" t="s">
-        <v>178</v>
+        <v>284</v>
       </c>
       <c r="H257" t="s">
-        <v>182</v>
+        <v>288</v>
       </c>
       <c r="K257">
         <v>30.66</v>
@@ -7022,13 +7340,13 @@
     </row>
     <row r="258" spans="6:15">
       <c r="F258" t="s">
-        <v>28</v>
+        <v>144</v>
       </c>
       <c r="G258" t="s">
-        <v>185</v>
+        <v>291</v>
       </c>
       <c r="H258" t="s">
-        <v>187</v>
+        <v>293</v>
       </c>
       <c r="K258">
         <v>398.66</v>
@@ -7045,13 +7363,13 @@
     </row>
     <row r="259" spans="6:15">
       <c r="F259" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G259" t="s">
-        <v>185</v>
+        <v>291</v>
       </c>
       <c r="H259" t="s">
-        <v>187</v>
+        <v>293</v>
       </c>
       <c r="K259">
         <v>348.66</v>
@@ -7068,13 +7386,13 @@
     </row>
     <row r="260" spans="6:15">
       <c r="F260" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G260" t="s">
-        <v>185</v>
+        <v>291</v>
       </c>
       <c r="H260" t="s">
-        <v>187</v>
+        <v>293</v>
       </c>
       <c r="K260">
         <v>229.33</v>
@@ -7091,13 +7409,13 @@
     </row>
     <row r="261" spans="6:15">
       <c r="F261" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G261" t="s">
-        <v>185</v>
+        <v>291</v>
       </c>
       <c r="H261" t="s">
-        <v>187</v>
+        <v>293</v>
       </c>
       <c r="K261">
         <v>996.66</v>
@@ -7114,13 +7432,13 @@
     </row>
     <row r="262" spans="6:15">
       <c r="F262" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="G262" t="s">
-        <v>178</v>
+        <v>284</v>
       </c>
       <c r="H262" t="s">
-        <v>182</v>
+        <v>288</v>
       </c>
       <c r="K262">
         <v>235.99</v>
@@ -7137,13 +7455,13 @@
     </row>
     <row r="263" spans="6:15">
       <c r="F263" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="G263" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="H263" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="K263">
         <v>370.66</v>
@@ -7160,13 +7478,13 @@
     </row>
     <row r="264" spans="6:15">
       <c r="F264" t="s">
-        <v>99</v>
+        <v>147</v>
       </c>
       <c r="G264" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="H264" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="K264">
         <v>374.66</v>
@@ -7183,13 +7501,13 @@
     </row>
     <row r="265" spans="6:15">
       <c r="F265" t="s">
-        <v>100</v>
+        <v>148</v>
       </c>
       <c r="G265" t="s">
-        <v>195</v>
+        <v>301</v>
       </c>
       <c r="H265" t="s">
-        <v>195</v>
+        <v>301</v>
       </c>
       <c r="K265">
         <v>1943.36</v>
@@ -7206,13 +7524,13 @@
     </row>
     <row r="266" spans="6:15">
       <c r="F266" t="s">
-        <v>101</v>
+        <v>149</v>
       </c>
       <c r="G266" t="s">
-        <v>195</v>
+        <v>301</v>
       </c>
       <c r="H266" t="s">
-        <v>195</v>
+        <v>301</v>
       </c>
       <c r="K266">
         <v>1133.36</v>
@@ -7229,13 +7547,13 @@
     </row>
     <row r="267" spans="6:15">
       <c r="F267" t="s">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="G267" t="s">
-        <v>210</v>
+        <v>316</v>
       </c>
       <c r="H267" t="s">
-        <v>230</v>
+        <v>336</v>
       </c>
       <c r="K267">
         <v>153.36</v>
@@ -7252,13 +7570,13 @@
     </row>
     <row r="268" spans="6:15">
       <c r="F268" t="s">
-        <v>22</v>
+        <v>151</v>
       </c>
       <c r="G268" t="s">
-        <v>168</v>
+        <v>274</v>
       </c>
       <c r="H268" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
       <c r="K268">
         <v>1213.36</v>
@@ -7275,13 +7593,13 @@
     </row>
     <row r="269" spans="6:15">
       <c r="F269" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="G269" t="s">
-        <v>209</v>
+        <v>315</v>
       </c>
       <c r="H269" t="s">
-        <v>216</v>
+        <v>322</v>
       </c>
       <c r="K269">
         <v>1060.08</v>
@@ -7298,13 +7616,13 @@
     </row>
     <row r="270" spans="6:15">
       <c r="F270" t="s">
-        <v>23</v>
+        <v>152</v>
       </c>
       <c r="G270" t="s">
-        <v>216</v>
+        <v>322</v>
       </c>
       <c r="H270" t="s">
-        <v>208</v>
+        <v>314</v>
       </c>
       <c r="K270">
         <v>280.67</v>
@@ -7321,13 +7639,13 @@
     </row>
     <row r="271" spans="6:15">
       <c r="F271" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G271" t="s">
-        <v>216</v>
+        <v>322</v>
       </c>
       <c r="H271" t="s">
-        <v>208</v>
+        <v>314</v>
       </c>
       <c r="K271">
         <v>1283.36</v>
@@ -7344,13 +7662,13 @@
     </row>
     <row r="272" spans="6:15">
       <c r="F272" t="s">
-        <v>103</v>
+        <v>153</v>
       </c>
       <c r="G272" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="H272" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="K272">
         <v>546.66</v>
@@ -7367,13 +7685,13 @@
     </row>
     <row r="273" spans="6:15">
       <c r="F273" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G273" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="H273" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="K273">
         <v>570.99</v>
@@ -7390,13 +7708,13 @@
     </row>
     <row r="274" spans="6:15">
       <c r="F274" t="s">
-        <v>104</v>
+        <v>154</v>
       </c>
       <c r="G274" t="s">
-        <v>154</v>
+        <v>260</v>
       </c>
       <c r="H274" t="s">
-        <v>143</v>
+        <v>249</v>
       </c>
       <c r="K274">
         <v>93.3</v>
@@ -7413,13 +7731,13 @@
     </row>
     <row r="275" spans="6:15">
       <c r="F275" t="s">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="G275" t="s">
-        <v>154</v>
+        <v>260</v>
       </c>
       <c r="H275" t="s">
-        <v>143</v>
+        <v>249</v>
       </c>
       <c r="K275">
         <v>211.95</v>
@@ -7436,13 +7754,13 @@
     </row>
     <row r="276" spans="6:15">
       <c r="F276" t="s">
-        <v>105</v>
+        <v>155</v>
       </c>
       <c r="G276" t="s">
-        <v>153</v>
+        <v>259</v>
       </c>
       <c r="H276" t="s">
-        <v>155</v>
+        <v>261</v>
       </c>
       <c r="K276">
         <v>418.65</v>
@@ -7459,13 +7777,13 @@
     </row>
     <row r="277" spans="6:15">
       <c r="F277" t="s">
-        <v>104</v>
+        <v>156</v>
       </c>
       <c r="G277" t="s">
-        <v>155</v>
+        <v>261</v>
       </c>
       <c r="H277" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="K277">
         <v>273.33</v>
@@ -7482,13 +7800,13 @@
     </row>
     <row r="278" spans="6:15">
       <c r="F278" t="s">
-        <v>104</v>
+        <v>157</v>
       </c>
       <c r="G278" t="s">
-        <v>155</v>
+        <v>261</v>
       </c>
       <c r="H278" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="K278">
         <v>179.33</v>
@@ -7505,13 +7823,13 @@
     </row>
     <row r="279" spans="6:15">
       <c r="F279" t="s">
-        <v>104</v>
+        <v>157</v>
       </c>
       <c r="G279" t="s">
-        <v>155</v>
+        <v>261</v>
       </c>
       <c r="H279" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="K279">
         <v>548.65</v>
@@ -7528,13 +7846,13 @@
     </row>
     <row r="280" spans="6:15">
       <c r="F280" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="G280" t="s">
-        <v>214</v>
+        <v>320</v>
       </c>
       <c r="H280" t="s">
-        <v>147</v>
+        <v>253</v>
       </c>
       <c r="K280">
         <v>356.02</v>
@@ -7551,13 +7869,13 @@
     </row>
     <row r="281" spans="6:15">
       <c r="F281" t="s">
-        <v>106</v>
+        <v>157</v>
       </c>
       <c r="G281" t="s">
-        <v>214</v>
+        <v>320</v>
       </c>
       <c r="H281" t="s">
-        <v>147</v>
+        <v>253</v>
       </c>
       <c r="K281">
         <v>265.34</v>
@@ -7574,13 +7892,13 @@
     </row>
     <row r="282" spans="6:15">
       <c r="F282" t="s">
-        <v>55</v>
+        <v>159</v>
       </c>
       <c r="G282" t="s">
-        <v>152</v>
+        <v>258</v>
       </c>
       <c r="H282" t="s">
-        <v>191</v>
+        <v>297</v>
       </c>
       <c r="K282">
         <v>74.66</v>
@@ -7597,13 +7915,13 @@
     </row>
     <row r="283" spans="6:15">
       <c r="F283" t="s">
-        <v>107</v>
+        <v>160</v>
       </c>
       <c r="G283" t="s">
-        <v>217</v>
+        <v>323</v>
       </c>
       <c r="H283" t="s">
-        <v>220</v>
+        <v>326</v>
       </c>
       <c r="K283">
         <v>179.32</v>
@@ -7620,13 +7938,13 @@
     </row>
     <row r="284" spans="6:15">
       <c r="F284" t="s">
-        <v>108</v>
+        <v>161</v>
       </c>
       <c r="G284" t="s">
-        <v>217</v>
+        <v>323</v>
       </c>
       <c r="H284" t="s">
-        <v>220</v>
+        <v>326</v>
       </c>
       <c r="K284">
         <v>219.32</v>
@@ -7643,13 +7961,13 @@
     </row>
     <row r="285" spans="6:15">
       <c r="F285" t="s">
-        <v>109</v>
+        <v>162</v>
       </c>
       <c r="G285" t="s">
-        <v>217</v>
+        <v>323</v>
       </c>
       <c r="H285" t="s">
-        <v>220</v>
+        <v>326</v>
       </c>
       <c r="K285">
         <v>199.32</v>
@@ -7666,13 +7984,13 @@
     </row>
     <row r="286" spans="6:15">
       <c r="F286" t="s">
-        <v>110</v>
+        <v>163</v>
       </c>
       <c r="G286" t="s">
-        <v>218</v>
+        <v>324</v>
       </c>
       <c r="H286" t="s">
-        <v>205</v>
+        <v>311</v>
       </c>
       <c r="K286">
         <v>823.3099999999999</v>
@@ -7689,13 +8007,13 @@
     </row>
     <row r="287" spans="6:15">
       <c r="F287" t="s">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="G287" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="H287" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="K287">
         <v>381.99</v>
@@ -7712,13 +8030,13 @@
     </row>
     <row r="288" spans="6:15">
       <c r="F288" t="s">
-        <v>90</v>
+        <v>137</v>
       </c>
       <c r="G288" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="H288" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="K288">
         <v>164.66</v>
@@ -7735,13 +8053,13 @@
     </row>
     <row r="289" spans="6:15">
       <c r="F289" t="s">
-        <v>111</v>
+        <v>165</v>
       </c>
       <c r="G289" t="s">
-        <v>218</v>
+        <v>324</v>
       </c>
       <c r="H289" t="s">
-        <v>205</v>
+        <v>311</v>
       </c>
       <c r="K289">
         <v>3.31</v>
@@ -7758,13 +8076,13 @@
     </row>
     <row r="290" spans="6:15">
       <c r="F290" t="s">
-        <v>44</v>
+        <v>166</v>
       </c>
       <c r="G290" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="H290" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="K290">
         <v>224.33</v>
@@ -7781,13 +8099,13 @@
     </row>
     <row r="291" spans="6:15">
       <c r="F291" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G291" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="H291" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="K291">
         <v>699.99</v>
@@ -7804,13 +8122,13 @@
     </row>
     <row r="292" spans="6:15">
       <c r="F292" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G292" t="s">
-        <v>159</v>
+        <v>265</v>
       </c>
       <c r="H292" t="s">
-        <v>160</v>
+        <v>266</v>
       </c>
       <c r="K292">
         <v>4495.99</v>
@@ -7827,13 +8145,13 @@
     </row>
     <row r="293" spans="6:15">
       <c r="F293" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G293" t="s">
-        <v>159</v>
+        <v>265</v>
       </c>
       <c r="H293" t="s">
-        <v>160</v>
+        <v>266</v>
       </c>
       <c r="K293">
         <v>2889.33</v>
@@ -7850,13 +8168,13 @@
     </row>
     <row r="294" spans="6:15">
       <c r="F294" t="s">
-        <v>112</v>
+        <v>167</v>
       </c>
       <c r="G294" t="s">
-        <v>205</v>
+        <v>311</v>
       </c>
       <c r="H294" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="K294">
         <v>363.99</v>
@@ -7873,13 +8191,13 @@
     </row>
     <row r="295" spans="6:15">
       <c r="F295" t="s">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="G295" t="s">
-        <v>218</v>
+        <v>324</v>
       </c>
       <c r="H295" t="s">
-        <v>205</v>
+        <v>311</v>
       </c>
       <c r="K295">
         <v>806.66</v>
@@ -7896,13 +8214,13 @@
     </row>
     <row r="296" spans="6:15">
       <c r="F296" t="s">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="G296" t="s">
-        <v>218</v>
+        <v>324</v>
       </c>
       <c r="H296" t="s">
-        <v>205</v>
+        <v>311</v>
       </c>
       <c r="K296">
         <v>798.66</v>
@@ -7919,13 +8237,13 @@
     </row>
     <row r="297" spans="6:15">
       <c r="F297" t="s">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="G297" t="s">
-        <v>218</v>
+        <v>324</v>
       </c>
       <c r="H297" t="s">
-        <v>205</v>
+        <v>311</v>
       </c>
       <c r="K297">
         <v>354.33</v>
@@ -7942,13 +8260,13 @@
     </row>
     <row r="298" spans="6:15">
       <c r="F298" t="s">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="G298" t="s">
-        <v>218</v>
+        <v>324</v>
       </c>
       <c r="H298" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="K298">
         <v>1696.66</v>
@@ -7965,13 +8283,13 @@
     </row>
     <row r="299" spans="6:15">
       <c r="F299" t="s">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="G299" t="s">
-        <v>157</v>
+        <v>263</v>
       </c>
       <c r="H299" t="s">
-        <v>154</v>
+        <v>260</v>
       </c>
       <c r="K299">
         <v>540.65</v>
@@ -7988,13 +8306,13 @@
     </row>
     <row r="300" spans="6:15">
       <c r="F300" t="s">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="G300" t="s">
-        <v>213</v>
+        <v>319</v>
       </c>
       <c r="H300" t="s">
-        <v>214</v>
+        <v>320</v>
       </c>
       <c r="K300">
         <v>7.01</v>
@@ -8011,13 +8329,13 @@
     </row>
     <row r="301" spans="6:15">
       <c r="F301" t="s">
-        <v>117</v>
+        <v>172</v>
       </c>
       <c r="G301" t="s">
-        <v>213</v>
+        <v>319</v>
       </c>
       <c r="H301" t="s">
-        <v>214</v>
+        <v>320</v>
       </c>
       <c r="K301">
         <v>4.67</v>
@@ -8034,13 +8352,13 @@
     </row>
     <row r="302" spans="6:15">
       <c r="F302" t="s">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="G302" t="s">
-        <v>190</v>
+        <v>296</v>
       </c>
       <c r="H302" t="s">
-        <v>199</v>
+        <v>305</v>
       </c>
       <c r="K302">
         <v>6.65</v>
@@ -8057,13 +8375,13 @@
     </row>
     <row r="303" spans="6:15">
       <c r="F303" t="s">
-        <v>97</v>
+        <v>174</v>
       </c>
       <c r="G303" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="H303" t="s">
-        <v>176</v>
+        <v>282</v>
       </c>
       <c r="K303">
         <v>111.66</v>
@@ -8080,13 +8398,13 @@
     </row>
     <row r="304" spans="6:15">
       <c r="F304" t="s">
-        <v>111</v>
+        <v>175</v>
       </c>
       <c r="G304" t="s">
-        <v>169</v>
+        <v>275</v>
       </c>
       <c r="H304" t="s">
-        <v>196</v>
+        <v>302</v>
       </c>
       <c r="K304">
         <v>530.65</v>
@@ -8103,13 +8421,13 @@
     </row>
     <row r="305" spans="6:15">
       <c r="F305" t="s">
-        <v>119</v>
+        <v>176</v>
       </c>
       <c r="G305" t="s">
-        <v>176</v>
+        <v>282</v>
       </c>
       <c r="H305" t="s">
-        <v>159</v>
+        <v>265</v>
       </c>
       <c r="K305">
         <v>77.33</v>
@@ -8126,13 +8444,13 @@
     </row>
     <row r="306" spans="6:15">
       <c r="F306" t="s">
-        <v>50</v>
+        <v>177</v>
       </c>
       <c r="G306" t="s">
-        <v>219</v>
+        <v>325</v>
       </c>
       <c r="H306" t="s">
-        <v>156</v>
+        <v>262</v>
       </c>
       <c r="K306">
         <v>0</v>
@@ -8149,13 +8467,13 @@
     </row>
     <row r="307" spans="6:15">
       <c r="F307" t="s">
-        <v>104</v>
+        <v>178</v>
       </c>
       <c r="G307" t="s">
-        <v>220</v>
+        <v>326</v>
       </c>
       <c r="H307" t="s">
-        <v>233</v>
+        <v>339</v>
       </c>
       <c r="K307">
         <v>278.65</v>
@@ -8172,13 +8490,13 @@
     </row>
     <row r="308" spans="6:15">
       <c r="F308" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="G308" t="s">
-        <v>220</v>
+        <v>326</v>
       </c>
       <c r="H308" t="s">
-        <v>233</v>
+        <v>339</v>
       </c>
       <c r="K308">
         <v>273.97</v>
@@ -8195,13 +8513,13 @@
     </row>
     <row r="309" spans="6:15">
       <c r="F309" t="s">
-        <v>89</v>
+        <v>180</v>
       </c>
       <c r="G309" t="s">
-        <v>153</v>
+        <v>259</v>
       </c>
       <c r="H309" t="s">
-        <v>155</v>
+        <v>261</v>
       </c>
       <c r="K309">
         <v>362.26</v>
@@ -8218,13 +8536,13 @@
     </row>
     <row r="310" spans="6:15">
       <c r="F310" t="s">
-        <v>90</v>
+        <v>137</v>
       </c>
       <c r="G310" t="s">
-        <v>153</v>
+        <v>259</v>
       </c>
       <c r="H310" t="s">
-        <v>155</v>
+        <v>261</v>
       </c>
       <c r="K310">
         <v>201.63</v>
@@ -8241,13 +8559,13 @@
     </row>
     <row r="311" spans="6:15">
       <c r="F311" t="s">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="G311" t="s">
-        <v>155</v>
+        <v>261</v>
       </c>
       <c r="H311" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="K311">
         <v>346.65</v>
@@ -8264,13 +8582,13 @@
     </row>
     <row r="312" spans="6:15">
       <c r="F312" t="s">
-        <v>27</v>
+        <v>182</v>
       </c>
       <c r="G312" t="s">
-        <v>180</v>
+        <v>286</v>
       </c>
       <c r="H312" t="s">
-        <v>151</v>
+        <v>257</v>
       </c>
       <c r="K312">
         <v>458.61</v>
@@ -8287,13 +8605,13 @@
     </row>
     <row r="313" spans="6:15">
       <c r="F313" t="s">
-        <v>107</v>
+        <v>183</v>
       </c>
       <c r="G313" t="s">
-        <v>155</v>
+        <v>261</v>
       </c>
       <c r="H313" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="K313">
         <v>348.65</v>
@@ -8310,13 +8628,13 @@
     </row>
     <row r="314" spans="6:15">
       <c r="F314" t="s">
-        <v>108</v>
+        <v>161</v>
       </c>
       <c r="G314" t="s">
-        <v>155</v>
+        <v>261</v>
       </c>
       <c r="H314" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="K314">
         <v>346.65</v>
@@ -8333,13 +8651,13 @@
     </row>
     <row r="315" spans="6:15">
       <c r="F315" t="s">
-        <v>121</v>
+        <v>184</v>
       </c>
       <c r="G315" t="s">
-        <v>151</v>
+        <v>257</v>
       </c>
       <c r="H315" t="s">
-        <v>150</v>
+        <v>256</v>
       </c>
       <c r="K315">
         <v>218.93</v>
@@ -8356,13 +8674,13 @@
     </row>
     <row r="316" spans="6:15">
       <c r="F316" t="s">
-        <v>95</v>
+        <v>142</v>
       </c>
       <c r="G316" t="s">
-        <v>151</v>
+        <v>257</v>
       </c>
       <c r="H316" t="s">
-        <v>150</v>
+        <v>256</v>
       </c>
       <c r="K316">
         <v>24.33</v>
@@ -8379,13 +8697,13 @@
     </row>
     <row r="317" spans="6:15">
       <c r="F317" t="s">
-        <v>95</v>
+        <v>142</v>
       </c>
       <c r="G317" t="s">
-        <v>151</v>
+        <v>257</v>
       </c>
       <c r="H317" t="s">
-        <v>222</v>
+        <v>328</v>
       </c>
       <c r="K317">
         <v>327.26</v>
@@ -8402,13 +8720,13 @@
     </row>
     <row r="318" spans="6:15">
       <c r="F318" t="s">
-        <v>77</v>
+        <v>185</v>
       </c>
       <c r="G318" t="s">
-        <v>150</v>
+        <v>256</v>
       </c>
       <c r="H318" t="s">
-        <v>198</v>
+        <v>304</v>
       </c>
       <c r="K318">
         <v>138.65</v>
@@ -8425,13 +8743,13 @@
     </row>
     <row r="319" spans="6:15">
       <c r="F319" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="G319" t="s">
-        <v>190</v>
+        <v>296</v>
       </c>
       <c r="H319" t="s">
-        <v>199</v>
+        <v>305</v>
       </c>
       <c r="K319">
         <v>594.65</v>
@@ -8448,13 +8766,13 @@
     </row>
     <row r="320" spans="6:15">
       <c r="F320" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="G320" t="s">
-        <v>143</v>
+        <v>249</v>
       </c>
       <c r="H320" t="s">
-        <v>180</v>
+        <v>286</v>
       </c>
       <c r="K320">
         <v>66.63</v>
@@ -8471,13 +8789,13 @@
     </row>
     <row r="321" spans="6:15">
       <c r="F321" t="s">
-        <v>15</v>
+        <v>186</v>
       </c>
       <c r="G321" t="s">
-        <v>157</v>
+        <v>263</v>
       </c>
       <c r="H321" t="s">
-        <v>154</v>
+        <v>260</v>
       </c>
       <c r="K321">
         <v>338.3</v>
@@ -8494,13 +8812,13 @@
     </row>
     <row r="322" spans="6:15">
       <c r="F322" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G322" t="s">
-        <v>190</v>
+        <v>296</v>
       </c>
       <c r="H322" t="s">
-        <v>199</v>
+        <v>305</v>
       </c>
       <c r="K322">
         <v>118.65</v>
@@ -8517,13 +8835,13 @@
     </row>
     <row r="323" spans="6:15">
       <c r="F323" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G323" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="H323" t="s">
-        <v>157</v>
+        <v>263</v>
       </c>
       <c r="K323">
         <v>513.3</v>
@@ -8543,10 +8861,10 @@
         <v>21</v>
       </c>
       <c r="G324" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="H324" t="s">
-        <v>157</v>
+        <v>263</v>
       </c>
       <c r="K324">
         <v>589.3</v>
@@ -8563,13 +8881,13 @@
     </row>
     <row r="325" spans="6:15">
       <c r="F325" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G325" t="s">
-        <v>187</v>
+        <v>293</v>
       </c>
       <c r="H325" t="s">
-        <v>221</v>
+        <v>327</v>
       </c>
       <c r="K325">
         <v>146.66</v>
@@ -8586,13 +8904,13 @@
     </row>
     <row r="326" spans="6:15">
       <c r="F326" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G326" t="s">
-        <v>187</v>
+        <v>293</v>
       </c>
       <c r="H326" t="s">
-        <v>225</v>
+        <v>331</v>
       </c>
       <c r="K326">
         <v>741.66</v>
@@ -8612,10 +8930,10 @@
         <v>21</v>
       </c>
       <c r="G327" t="s">
-        <v>187</v>
+        <v>293</v>
       </c>
       <c r="H327" t="s">
-        <v>225</v>
+        <v>331</v>
       </c>
       <c r="K327">
         <v>308.66</v>
@@ -8635,10 +8953,10 @@
         <v>21</v>
       </c>
       <c r="G328" t="s">
-        <v>187</v>
+        <v>293</v>
       </c>
       <c r="H328" t="s">
-        <v>225</v>
+        <v>331</v>
       </c>
       <c r="K328">
         <v>173.33</v>
@@ -8655,13 +8973,13 @@
     </row>
     <row r="329" spans="6:15">
       <c r="F329" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G329" t="s">
-        <v>221</v>
+        <v>327</v>
       </c>
       <c r="H329" t="s">
-        <v>149</v>
+        <v>255</v>
       </c>
       <c r="K329">
         <v>277.33</v>
@@ -8678,13 +8996,13 @@
     </row>
     <row r="330" spans="6:15">
       <c r="F330" t="s">
-        <v>25</v>
+        <v>187</v>
       </c>
       <c r="G330" t="s">
-        <v>221</v>
+        <v>327</v>
       </c>
       <c r="H330" t="s">
-        <v>149</v>
+        <v>255</v>
       </c>
       <c r="K330">
         <v>681.3099999999999</v>
@@ -8701,13 +9019,13 @@
     </row>
     <row r="331" spans="6:15">
       <c r="F331" t="s">
-        <v>23</v>
+        <v>188</v>
       </c>
       <c r="G331" t="s">
-        <v>152</v>
+        <v>258</v>
       </c>
       <c r="H331" t="s">
-        <v>191</v>
+        <v>297</v>
       </c>
       <c r="K331">
         <v>428.66</v>
@@ -8724,13 +9042,13 @@
     </row>
     <row r="332" spans="6:15">
       <c r="F332" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G332" t="s">
-        <v>152</v>
+        <v>258</v>
       </c>
       <c r="H332" t="s">
-        <v>191</v>
+        <v>297</v>
       </c>
       <c r="K332">
         <v>235.33</v>
@@ -8747,13 +9065,13 @@
     </row>
     <row r="333" spans="6:15">
       <c r="F333" t="s">
-        <v>23</v>
+        <v>189</v>
       </c>
       <c r="G333" t="s">
-        <v>152</v>
+        <v>258</v>
       </c>
       <c r="H333" t="s">
-        <v>191</v>
+        <v>297</v>
       </c>
       <c r="K333">
         <v>309.33</v>
@@ -8770,13 +9088,13 @@
     </row>
     <row r="334" spans="6:15">
       <c r="F334" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G334" t="s">
-        <v>152</v>
+        <v>258</v>
       </c>
       <c r="H334" t="s">
-        <v>191</v>
+        <v>297</v>
       </c>
       <c r="K334">
         <v>399.33</v>
@@ -8793,13 +9111,13 @@
     </row>
     <row r="335" spans="6:15">
       <c r="F335" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G335" t="s">
-        <v>152</v>
+        <v>258</v>
       </c>
       <c r="H335" t="s">
-        <v>191</v>
+        <v>297</v>
       </c>
       <c r="K335">
         <v>960.66</v>
@@ -8816,13 +9134,13 @@
     </row>
     <row r="336" spans="6:15">
       <c r="F336" t="s">
-        <v>23</v>
+        <v>189</v>
       </c>
       <c r="G336" t="s">
-        <v>221</v>
+        <v>327</v>
       </c>
       <c r="H336" t="s">
-        <v>149</v>
+        <v>255</v>
       </c>
       <c r="K336">
         <v>198.66</v>
@@ -8839,13 +9157,13 @@
     </row>
     <row r="337" spans="6:15">
       <c r="F337" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G337" t="s">
-        <v>221</v>
+        <v>327</v>
       </c>
       <c r="H337" t="s">
-        <v>149</v>
+        <v>255</v>
       </c>
       <c r="K337">
         <v>497.33</v>
@@ -8862,13 +9180,13 @@
     </row>
     <row r="338" spans="6:15">
       <c r="F338" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G338" t="s">
-        <v>221</v>
+        <v>327</v>
       </c>
       <c r="H338" t="s">
-        <v>227</v>
+        <v>333</v>
       </c>
       <c r="K338">
         <v>45.33</v>
@@ -8885,13 +9203,13 @@
     </row>
     <row r="339" spans="6:15">
       <c r="F339" t="s">
-        <v>122</v>
+        <v>190</v>
       </c>
       <c r="G339" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="H339" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="K339">
         <v>33.31</v>
@@ -8908,13 +9226,13 @@
     </row>
     <row r="340" spans="6:15">
       <c r="F340" t="s">
-        <v>42</v>
+        <v>191</v>
       </c>
       <c r="G340" t="s">
-        <v>205</v>
+        <v>311</v>
       </c>
       <c r="H340" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="K340">
         <v>82.66</v>
@@ -8931,13 +9249,13 @@
     </row>
     <row r="341" spans="6:15">
       <c r="F341" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="G341" t="s">
-        <v>205</v>
+        <v>311</v>
       </c>
       <c r="H341" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="K341">
         <v>120.99</v>
@@ -8954,13 +9272,13 @@
     </row>
     <row r="342" spans="6:15">
       <c r="F342" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="G342" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="H342" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="K342">
         <v>238.66</v>
@@ -8977,13 +9295,13 @@
     </row>
     <row r="343" spans="6:15">
       <c r="F343" t="s">
-        <v>15</v>
+        <v>192</v>
       </c>
       <c r="G343" t="s">
-        <v>155</v>
+        <v>261</v>
       </c>
       <c r="H343" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="K343">
         <v>438.65</v>
@@ -9000,13 +9318,13 @@
     </row>
     <row r="344" spans="6:15">
       <c r="F344" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G344" t="s">
-        <v>222</v>
+        <v>328</v>
       </c>
       <c r="H344" t="s">
-        <v>145</v>
+        <v>251</v>
       </c>
       <c r="K344">
         <v>497.3</v>
@@ -9026,10 +9344,10 @@
         <v>21</v>
       </c>
       <c r="G345" t="s">
-        <v>223</v>
+        <v>329</v>
       </c>
       <c r="H345" t="s">
-        <v>190</v>
+        <v>296</v>
       </c>
       <c r="K345">
         <v>238.65</v>
@@ -9049,10 +9367,10 @@
         <v>21</v>
       </c>
       <c r="G346" t="s">
-        <v>223</v>
+        <v>329</v>
       </c>
       <c r="H346" t="s">
-        <v>190</v>
+        <v>296</v>
       </c>
       <c r="K346">
         <v>384.65</v>
@@ -9069,13 +9387,13 @@
     </row>
     <row r="347" spans="6:15">
       <c r="F347" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G347" t="s">
-        <v>190</v>
+        <v>296</v>
       </c>
       <c r="H347" t="s">
-        <v>199</v>
+        <v>305</v>
       </c>
       <c r="K347">
         <v>18.65</v>
@@ -9092,13 +9410,13 @@
     </row>
     <row r="348" spans="6:15">
       <c r="F348" t="s">
-        <v>32</v>
+        <v>118</v>
       </c>
       <c r="G348" t="s">
-        <v>158</v>
+        <v>264</v>
       </c>
       <c r="H348" t="s">
-        <v>234</v>
+        <v>340</v>
       </c>
       <c r="K348">
         <v>168.34</v>
@@ -9118,10 +9436,10 @@
         <v>21</v>
       </c>
       <c r="G349" t="s">
-        <v>158</v>
+        <v>264</v>
       </c>
       <c r="H349" t="s">
-        <v>213</v>
+        <v>319</v>
       </c>
       <c r="K349">
         <v>398.67</v>
@@ -9141,10 +9459,10 @@
         <v>21</v>
       </c>
       <c r="G350" t="s">
-        <v>158</v>
+        <v>264</v>
       </c>
       <c r="H350" t="s">
-        <v>213</v>
+        <v>319</v>
       </c>
       <c r="K350">
         <v>448.01</v>
@@ -9164,10 +9482,10 @@
         <v>21</v>
       </c>
       <c r="G351" t="s">
-        <v>158</v>
+        <v>264</v>
       </c>
       <c r="H351" t="s">
-        <v>214</v>
+        <v>320</v>
       </c>
       <c r="K351">
         <v>275.68</v>
@@ -9184,13 +9502,13 @@
     </row>
     <row r="352" spans="6:15">
       <c r="F352" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G352" t="s">
-        <v>222</v>
+        <v>328</v>
       </c>
       <c r="H352" t="s">
-        <v>223</v>
+        <v>329</v>
       </c>
       <c r="K352">
         <v>156.28</v>
@@ -9207,13 +9525,13 @@
     </row>
     <row r="353" spans="6:15">
       <c r="F353" t="s">
-        <v>77</v>
+        <v>193</v>
       </c>
       <c r="G353" t="s">
-        <v>191</v>
+        <v>297</v>
       </c>
       <c r="H353" t="s">
-        <v>185</v>
+        <v>291</v>
       </c>
       <c r="K353">
         <v>136.66</v>
@@ -9230,13 +9548,13 @@
     </row>
     <row r="354" spans="6:15">
       <c r="F354" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="G354" t="s">
-        <v>191</v>
+        <v>297</v>
       </c>
       <c r="H354" t="s">
-        <v>185</v>
+        <v>291</v>
       </c>
       <c r="K354">
         <v>261.66</v>
@@ -9253,13 +9571,13 @@
     </row>
     <row r="355" spans="6:15">
       <c r="F355" t="s">
-        <v>50</v>
+        <v>194</v>
       </c>
       <c r="G355" t="s">
-        <v>144</v>
+        <v>250</v>
       </c>
       <c r="H355" t="s">
-        <v>184</v>
+        <v>290</v>
       </c>
       <c r="K355">
         <v>360.66</v>
@@ -9276,13 +9594,13 @@
     </row>
     <row r="356" spans="6:15">
       <c r="F356" t="s">
-        <v>32</v>
+        <v>195</v>
       </c>
       <c r="G356" t="s">
-        <v>182</v>
+        <v>288</v>
       </c>
       <c r="H356" t="s">
-        <v>144</v>
+        <v>250</v>
       </c>
       <c r="K356">
         <v>540.33</v>
@@ -9302,10 +9620,10 @@
         <v>21</v>
       </c>
       <c r="G357" t="s">
-        <v>182</v>
+        <v>288</v>
       </c>
       <c r="H357" t="s">
-        <v>144</v>
+        <v>250</v>
       </c>
       <c r="K357">
         <v>1597.33</v>
@@ -9325,10 +9643,10 @@
         <v>21</v>
       </c>
       <c r="G358" t="s">
-        <v>182</v>
+        <v>288</v>
       </c>
       <c r="H358" t="s">
-        <v>144</v>
+        <v>250</v>
       </c>
       <c r="K358">
         <v>1871.66</v>
@@ -9345,13 +9663,13 @@
     </row>
     <row r="359" spans="6:15">
       <c r="F359" t="s">
-        <v>32</v>
+        <v>118</v>
       </c>
       <c r="G359" t="s">
-        <v>144</v>
+        <v>250</v>
       </c>
       <c r="H359" t="s">
-        <v>184</v>
+        <v>290</v>
       </c>
       <c r="K359">
         <v>99.33</v>
@@ -9371,10 +9689,10 @@
         <v>21</v>
       </c>
       <c r="G360" t="s">
-        <v>144</v>
+        <v>250</v>
       </c>
       <c r="H360" t="s">
-        <v>184</v>
+        <v>290</v>
       </c>
       <c r="K360">
         <v>99.33</v>
@@ -9394,10 +9712,10 @@
         <v>21</v>
       </c>
       <c r="G361" t="s">
-        <v>144</v>
+        <v>250</v>
       </c>
       <c r="H361" t="s">
-        <v>184</v>
+        <v>290</v>
       </c>
       <c r="K361">
         <v>317.33</v>
@@ -9414,13 +9732,13 @@
     </row>
     <row r="362" spans="6:15">
       <c r="F362" t="s">
-        <v>40</v>
+        <v>196</v>
       </c>
       <c r="G362" t="s">
-        <v>224</v>
+        <v>330</v>
       </c>
       <c r="H362" t="s">
-        <v>235</v>
+        <v>341</v>
       </c>
       <c r="K362">
         <v>0</v>
@@ -9437,13 +9755,13 @@
     </row>
     <row r="363" spans="6:15">
       <c r="F363" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G363" t="s">
-        <v>224</v>
+        <v>330</v>
       </c>
       <c r="H363" t="s">
-        <v>235</v>
+        <v>341</v>
       </c>
       <c r="K363">
         <v>0</v>
@@ -9460,13 +9778,13 @@
     </row>
     <row r="364" spans="6:15">
       <c r="F364" t="s">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="G364" t="s">
-        <v>187</v>
+        <v>293</v>
       </c>
       <c r="H364" t="s">
-        <v>225</v>
+        <v>331</v>
       </c>
       <c r="K364">
         <v>541.66</v>
@@ -9483,13 +9801,13 @@
     </row>
     <row r="365" spans="6:15">
       <c r="F365" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G365" t="s">
-        <v>187</v>
+        <v>293</v>
       </c>
       <c r="H365" t="s">
-        <v>225</v>
+        <v>331</v>
       </c>
       <c r="K365">
         <v>119.33</v>
@@ -9506,13 +9824,13 @@
     </row>
     <row r="366" spans="6:15">
       <c r="F366" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G366" t="s">
-        <v>187</v>
+        <v>293</v>
       </c>
       <c r="H366" t="s">
-        <v>225</v>
+        <v>331</v>
       </c>
       <c r="K366">
         <v>119.33</v>
@@ -9529,13 +9847,13 @@
     </row>
     <row r="367" spans="6:15">
       <c r="F367" t="s">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="G367" t="s">
-        <v>221</v>
+        <v>327</v>
       </c>
       <c r="H367" t="s">
-        <v>149</v>
+        <v>255</v>
       </c>
       <c r="K367">
         <v>197.33</v>
@@ -9552,13 +9870,13 @@
     </row>
     <row r="368" spans="6:15">
       <c r="F368" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="G368" t="s">
-        <v>221</v>
+        <v>327</v>
       </c>
       <c r="H368" t="s">
-        <v>236</v>
+        <v>342</v>
       </c>
       <c r="K368">
         <v>0</v>
@@ -9575,13 +9893,13 @@
     </row>
     <row r="369" spans="6:15">
       <c r="F369" t="s">
-        <v>123</v>
+        <v>198</v>
       </c>
       <c r="G369" t="s">
-        <v>225</v>
+        <v>331</v>
       </c>
       <c r="H369" t="s">
-        <v>221</v>
+        <v>327</v>
       </c>
       <c r="K369">
         <v>346.66</v>
@@ -9598,13 +9916,13 @@
     </row>
     <row r="370" spans="6:15">
       <c r="F370" t="s">
-        <v>124</v>
+        <v>199</v>
       </c>
       <c r="G370" t="s">
-        <v>225</v>
+        <v>331</v>
       </c>
       <c r="H370" t="s">
-        <v>221</v>
+        <v>327</v>
       </c>
       <c r="K370">
         <v>488.66</v>
@@ -9621,13 +9939,13 @@
     </row>
     <row r="371" spans="6:15">
       <c r="F371" t="s">
-        <v>47</v>
+        <v>200</v>
       </c>
       <c r="G371" t="s">
-        <v>187</v>
+        <v>293</v>
       </c>
       <c r="H371" t="s">
-        <v>236</v>
+        <v>342</v>
       </c>
       <c r="K371">
         <v>0</v>
@@ -9644,13 +9962,13 @@
     </row>
     <row r="372" spans="6:15">
       <c r="F372" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="G372" t="s">
-        <v>144</v>
+        <v>250</v>
       </c>
       <c r="H372" t="s">
-        <v>152</v>
+        <v>258</v>
       </c>
       <c r="K372">
         <v>203.31</v>
@@ -9667,13 +9985,13 @@
     </row>
     <row r="373" spans="6:15">
       <c r="F373" t="s">
-        <v>28</v>
+        <v>144</v>
       </c>
       <c r="G373" t="s">
-        <v>186</v>
+        <v>292</v>
       </c>
       <c r="H373" t="s">
-        <v>178</v>
+        <v>284</v>
       </c>
       <c r="K373">
         <v>636.99</v>
@@ -9690,13 +10008,13 @@
     </row>
     <row r="374" spans="6:15">
       <c r="F374" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G374" t="s">
-        <v>186</v>
+        <v>292</v>
       </c>
       <c r="H374" t="s">
-        <v>178</v>
+        <v>284</v>
       </c>
       <c r="K374">
         <v>438.66</v>
@@ -9713,13 +10031,13 @@
     </row>
     <row r="375" spans="6:15">
       <c r="F375" t="s">
-        <v>42</v>
+        <v>201</v>
       </c>
       <c r="G375" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="H375" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="K375">
         <v>234.99</v>
@@ -9736,13 +10054,13 @@
     </row>
     <row r="376" spans="6:15">
       <c r="F376" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="G376" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="H376" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="K376">
         <v>154.66</v>
@@ -9759,13 +10077,13 @@
     </row>
     <row r="377" spans="6:15">
       <c r="F377" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="G377" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="H377" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="K377">
         <v>441.99</v>
@@ -9782,13 +10100,13 @@
     </row>
     <row r="378" spans="6:15">
       <c r="F378" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="G378" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="H378" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="K378">
         <v>125.33</v>
@@ -9805,13 +10123,13 @@
     </row>
     <row r="379" spans="6:15">
       <c r="F379" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="G379" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="H379" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="K379">
         <v>200.66</v>
@@ -9828,13 +10146,13 @@
     </row>
     <row r="380" spans="6:15">
       <c r="F380" t="s">
-        <v>48</v>
+        <v>202</v>
       </c>
       <c r="G380" t="s">
-        <v>218</v>
+        <v>324</v>
       </c>
       <c r="H380" t="s">
-        <v>205</v>
+        <v>311</v>
       </c>
       <c r="K380">
         <v>506.66</v>
@@ -9851,13 +10169,13 @@
     </row>
     <row r="381" spans="6:15">
       <c r="F381" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G381" t="s">
-        <v>218</v>
+        <v>324</v>
       </c>
       <c r="H381" t="s">
-        <v>205</v>
+        <v>311</v>
       </c>
       <c r="K381">
         <v>553.3099999999999</v>
@@ -9874,13 +10192,13 @@
     </row>
     <row r="382" spans="6:15">
       <c r="F382" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G382" t="s">
-        <v>218</v>
+        <v>324</v>
       </c>
       <c r="H382" t="s">
-        <v>205</v>
+        <v>311</v>
       </c>
       <c r="K382">
         <v>1486.63</v>
@@ -9897,13 +10215,13 @@
     </row>
     <row r="383" spans="6:15">
       <c r="F383" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G383" t="s">
-        <v>218</v>
+        <v>324</v>
       </c>
       <c r="H383" t="s">
-        <v>205</v>
+        <v>311</v>
       </c>
       <c r="K383">
         <v>346.66</v>
@@ -9920,13 +10238,13 @@
     </row>
     <row r="384" spans="6:15">
       <c r="F384" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G384" t="s">
-        <v>218</v>
+        <v>324</v>
       </c>
       <c r="H384" t="s">
-        <v>205</v>
+        <v>311</v>
       </c>
       <c r="K384">
         <v>393.31</v>
@@ -9943,13 +10261,13 @@
     </row>
     <row r="385" spans="6:15">
       <c r="F385" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G385" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="H385" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="K385">
         <v>138.66</v>
@@ -9966,13 +10284,13 @@
     </row>
     <row r="386" spans="6:15">
       <c r="F386" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G386" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="H386" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="K386">
         <v>543.3099999999999</v>
@@ -9989,13 +10307,13 @@
     </row>
     <row r="387" spans="6:15">
       <c r="F387" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G387" t="s">
-        <v>205</v>
+        <v>311</v>
       </c>
       <c r="H387" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="K387">
         <v>666.63</v>
@@ -10012,13 +10330,13 @@
     </row>
     <row r="388" spans="6:15">
       <c r="F388" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G388" t="s">
-        <v>205</v>
+        <v>311</v>
       </c>
       <c r="H388" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="K388">
         <v>586.63</v>
@@ -10035,13 +10353,13 @@
     </row>
     <row r="389" spans="6:15">
       <c r="F389" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G389" t="s">
-        <v>205</v>
+        <v>311</v>
       </c>
       <c r="H389" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="K389">
         <v>313.31</v>
@@ -10058,13 +10376,13 @@
     </row>
     <row r="390" spans="6:15">
       <c r="F390" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G390" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="H390" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="K390">
         <v>293.31</v>
@@ -10081,13 +10399,13 @@
     </row>
     <row r="391" spans="6:15">
       <c r="F391" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G391" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="H391" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="K391">
         <v>223.31</v>
@@ -10104,13 +10422,13 @@
     </row>
     <row r="392" spans="6:15">
       <c r="F392" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G392" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="H392" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="K392">
         <v>293.31</v>
@@ -10127,13 +10445,13 @@
     </row>
     <row r="393" spans="6:15">
       <c r="F393" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G393" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="H393" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="K393">
         <v>293.31</v>
@@ -10150,13 +10468,13 @@
     </row>
     <row r="394" spans="6:15">
       <c r="F394" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G394" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="H394" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="K394">
         <v>73.31</v>
@@ -10173,13 +10491,13 @@
     </row>
     <row r="395" spans="6:15">
       <c r="F395" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="G395" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="H395" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="K395">
         <v>323.31</v>
@@ -10196,13 +10514,13 @@
     </row>
     <row r="396" spans="6:15">
       <c r="F396" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="G396" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="H396" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="K396">
         <v>273.31</v>
@@ -10219,13 +10537,13 @@
     </row>
     <row r="397" spans="6:15">
       <c r="F397" t="s">
-        <v>44</v>
+        <v>203</v>
       </c>
       <c r="G397" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="H397" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="K397">
         <v>350.66</v>
@@ -10242,13 +10560,13 @@
     </row>
     <row r="398" spans="6:15">
       <c r="F398" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="G398" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="H398" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="K398">
         <v>794.66</v>
@@ -10265,13 +10583,13 @@
     </row>
     <row r="399" spans="6:15">
       <c r="F399" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="G399" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="H399" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="K399">
         <v>329.33</v>
@@ -10288,13 +10606,13 @@
     </row>
     <row r="400" spans="6:15">
       <c r="F400" t="s">
-        <v>44</v>
+        <v>203</v>
       </c>
       <c r="G400" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="H400" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="K400">
         <v>161.33</v>
@@ -10311,13 +10629,13 @@
     </row>
     <row r="401" spans="6:15">
       <c r="F401" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="G401" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="H401" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="K401">
         <v>161.33</v>
@@ -10334,13 +10652,13 @@
     </row>
     <row r="402" spans="6:15">
       <c r="F402" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="G402" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="H402" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="K402">
         <v>212.66</v>
@@ -10357,13 +10675,13 @@
     </row>
     <row r="403" spans="6:15">
       <c r="F403" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="G403" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="H403" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="K403">
         <v>141.33</v>
@@ -10380,13 +10698,13 @@
     </row>
     <row r="404" spans="6:15">
       <c r="F404" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="G404" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="H404" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="K404">
         <v>897.99</v>
@@ -10403,13 +10721,13 @@
     </row>
     <row r="405" spans="6:15">
       <c r="F405" t="s">
-        <v>44</v>
+        <v>203</v>
       </c>
       <c r="G405" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="H405" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="K405">
         <v>259.33</v>
@@ -10426,13 +10744,13 @@
     </row>
     <row r="406" spans="6:15">
       <c r="F406" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="G406" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="H406" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="K406">
         <v>134.33</v>
@@ -10449,13 +10767,13 @@
     </row>
     <row r="407" spans="6:15">
       <c r="F407" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="G407" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="H407" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="K407">
         <v>174.33</v>
@@ -10472,13 +10790,13 @@
     </row>
     <row r="408" spans="6:15">
       <c r="F408" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="G408" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="H408" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="K408">
         <v>254.66</v>
@@ -10495,13 +10813,13 @@
     </row>
     <row r="409" spans="6:15">
       <c r="F409" t="s">
-        <v>125</v>
+        <v>204</v>
       </c>
       <c r="G409" t="s">
-        <v>226</v>
+        <v>332</v>
       </c>
       <c r="H409" t="s">
-        <v>202</v>
+        <v>308</v>
       </c>
       <c r="K409">
         <v>139</v>
@@ -10518,13 +10836,13 @@
     </row>
     <row r="410" spans="6:15">
       <c r="F410" t="s">
-        <v>125</v>
+        <v>57</v>
       </c>
       <c r="G410" t="s">
-        <v>226</v>
+        <v>332</v>
       </c>
       <c r="H410" t="s">
-        <v>202</v>
+        <v>308</v>
       </c>
       <c r="K410">
         <v>266.66</v>
@@ -10541,13 +10859,13 @@
     </row>
     <row r="411" spans="6:15">
       <c r="F411" t="s">
-        <v>125</v>
+        <v>57</v>
       </c>
       <c r="G411" t="s">
-        <v>226</v>
+        <v>332</v>
       </c>
       <c r="H411" t="s">
-        <v>202</v>
+        <v>308</v>
       </c>
       <c r="K411">
         <v>46.33</v>
@@ -10564,13 +10882,13 @@
     </row>
     <row r="412" spans="6:15">
       <c r="F412" t="s">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="G412" t="s">
-        <v>205</v>
+        <v>311</v>
       </c>
       <c r="H412" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="K412">
         <v>446.63</v>
@@ -10587,13 +10905,13 @@
     </row>
     <row r="413" spans="6:15">
       <c r="F413" t="s">
-        <v>23</v>
+        <v>189</v>
       </c>
       <c r="G413" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="H413" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="K413">
         <v>234.99</v>
@@ -10610,13 +10928,13 @@
     </row>
     <row r="414" spans="6:15">
       <c r="F414" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G414" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="H414" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="K414">
         <v>148.66</v>
@@ -10633,13 +10951,13 @@
     </row>
     <row r="415" spans="6:15">
       <c r="F415" t="s">
-        <v>126</v>
+        <v>205</v>
       </c>
       <c r="G415" t="s">
-        <v>184</v>
+        <v>290</v>
       </c>
       <c r="H415" t="s">
-        <v>191</v>
+        <v>297</v>
       </c>
       <c r="K415">
         <v>146.66</v>
@@ -10656,13 +10974,13 @@
     </row>
     <row r="416" spans="6:15">
       <c r="F416" t="s">
-        <v>45</v>
+        <v>206</v>
       </c>
       <c r="G416" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="H416" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="K416">
         <v>1238.66</v>
@@ -10679,13 +10997,13 @@
     </row>
     <row r="417" spans="6:15">
       <c r="F417" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G417" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="H417" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="K417">
         <v>526.66</v>
@@ -10702,13 +11020,13 @@
     </row>
     <row r="418" spans="6:15">
       <c r="F418" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G418" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="H418" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="K418">
         <v>816.33</v>
@@ -10725,13 +11043,13 @@
     </row>
     <row r="419" spans="6:15">
       <c r="F419" t="s">
-        <v>127</v>
+        <v>207</v>
       </c>
       <c r="G419" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="H419" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="K419">
         <v>496.66</v>
@@ -10748,13 +11066,13 @@
     </row>
     <row r="420" spans="6:15">
       <c r="F420" t="s">
-        <v>90</v>
+        <v>137</v>
       </c>
       <c r="G420" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="H420" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="K420">
         <v>341.66</v>
@@ -10771,13 +11089,13 @@
     </row>
     <row r="421" spans="6:15">
       <c r="F421" t="s">
-        <v>90</v>
+        <v>137</v>
       </c>
       <c r="G421" t="s">
-        <v>159</v>
+        <v>265</v>
       </c>
       <c r="H421" t="s">
-        <v>192</v>
+        <v>298</v>
       </c>
       <c r="K421">
         <v>441.33</v>
@@ -10794,13 +11112,13 @@
     </row>
     <row r="422" spans="6:15">
       <c r="F422" t="s">
-        <v>90</v>
+        <v>137</v>
       </c>
       <c r="G422" t="s">
-        <v>160</v>
+        <v>266</v>
       </c>
       <c r="H422" t="s">
-        <v>193</v>
+        <v>299</v>
       </c>
       <c r="K422">
         <v>966.97</v>
@@ -10817,13 +11135,13 @@
     </row>
     <row r="423" spans="6:15">
       <c r="F423" t="s">
-        <v>128</v>
+        <v>208</v>
       </c>
       <c r="G423" t="s">
-        <v>149</v>
+        <v>255</v>
       </c>
       <c r="H423" t="s">
-        <v>227</v>
+        <v>333</v>
       </c>
       <c r="K423">
         <v>431.66</v>
@@ -10840,13 +11158,13 @@
     </row>
     <row r="424" spans="6:15">
       <c r="F424" t="s">
-        <v>128</v>
+        <v>209</v>
       </c>
       <c r="G424" t="s">
-        <v>186</v>
+        <v>292</v>
       </c>
       <c r="H424" t="s">
-        <v>211</v>
+        <v>317</v>
       </c>
       <c r="K424">
         <v>577.33</v>
@@ -10863,13 +11181,13 @@
     </row>
     <row r="425" spans="6:15">
       <c r="F425" t="s">
-        <v>129</v>
+        <v>210</v>
       </c>
       <c r="G425" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="H425" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="K425">
         <v>58.66</v>
@@ -10886,13 +11204,13 @@
     </row>
     <row r="426" spans="6:15">
       <c r="F426" t="s">
-        <v>130</v>
+        <v>211</v>
       </c>
       <c r="G426" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="H426" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="K426">
         <v>442.66</v>
@@ -10909,13 +11227,13 @@
     </row>
     <row r="427" spans="6:15">
       <c r="F427" t="s">
-        <v>130</v>
+        <v>211</v>
       </c>
       <c r="G427" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="H427" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="K427">
         <v>101.33</v>
@@ -10932,13 +11250,13 @@
     </row>
     <row r="428" spans="6:15">
       <c r="F428" t="s">
-        <v>44</v>
+        <v>212</v>
       </c>
       <c r="G428" t="s">
-        <v>193</v>
+        <v>299</v>
       </c>
       <c r="H428" t="s">
-        <v>193</v>
+        <v>299</v>
       </c>
       <c r="K428">
         <v>563.3099999999999</v>
@@ -10955,13 +11273,13 @@
     </row>
     <row r="429" spans="6:15">
       <c r="F429" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="G429" t="s">
-        <v>193</v>
+        <v>299</v>
       </c>
       <c r="H429" t="s">
-        <v>193</v>
+        <v>299</v>
       </c>
       <c r="K429">
         <v>56.33</v>
@@ -10978,13 +11296,13 @@
     </row>
     <row r="430" spans="6:15">
       <c r="F430" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="G430" t="s">
-        <v>193</v>
+        <v>299</v>
       </c>
       <c r="H430" t="s">
-        <v>193</v>
+        <v>299</v>
       </c>
       <c r="K430">
         <v>1408.29</v>
@@ -11001,13 +11319,13 @@
     </row>
     <row r="431" spans="6:15">
       <c r="F431" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="G431" t="s">
-        <v>161</v>
+        <v>267</v>
       </c>
       <c r="H431" t="s">
-        <v>167</v>
+        <v>273</v>
       </c>
       <c r="K431">
         <v>196.66</v>
@@ -11024,13 +11342,13 @@
     </row>
     <row r="432" spans="6:15">
       <c r="F432" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G432" t="s">
-        <v>161</v>
+        <v>267</v>
       </c>
       <c r="H432" t="s">
-        <v>167</v>
+        <v>273</v>
       </c>
       <c r="K432">
         <v>126.66</v>
@@ -11047,13 +11365,13 @@
     </row>
     <row r="433" spans="6:15">
       <c r="F433" t="s">
-        <v>125</v>
+        <v>213</v>
       </c>
       <c r="G433" t="s">
-        <v>226</v>
+        <v>332</v>
       </c>
       <c r="H433" t="s">
-        <v>202</v>
+        <v>308</v>
       </c>
       <c r="K433">
         <v>171.66</v>
@@ -11070,13 +11388,13 @@
     </row>
     <row r="434" spans="6:15">
       <c r="F434" t="s">
-        <v>131</v>
+        <v>214</v>
       </c>
       <c r="G434" t="s">
-        <v>226</v>
+        <v>332</v>
       </c>
       <c r="H434" t="s">
-        <v>202</v>
+        <v>308</v>
       </c>
       <c r="K434">
         <v>606.63</v>
@@ -11093,13 +11411,13 @@
     </row>
     <row r="435" spans="6:15">
       <c r="F435" t="s">
-        <v>77</v>
+        <v>215</v>
       </c>
       <c r="G435" t="s">
-        <v>161</v>
+        <v>267</v>
       </c>
       <c r="H435" t="s">
-        <v>167</v>
+        <v>273</v>
       </c>
       <c r="K435">
         <v>73.31</v>
@@ -11116,13 +11434,13 @@
     </row>
     <row r="436" spans="6:15">
       <c r="F436" t="s">
-        <v>132</v>
+        <v>216</v>
       </c>
       <c r="G436" t="s">
-        <v>201</v>
+        <v>307</v>
       </c>
       <c r="H436" t="s">
-        <v>178</v>
+        <v>284</v>
       </c>
       <c r="K436">
         <v>378.66</v>
@@ -11139,13 +11457,13 @@
     </row>
     <row r="437" spans="6:15">
       <c r="F437" t="s">
-        <v>55</v>
+        <v>217</v>
       </c>
       <c r="G437" t="s">
-        <v>161</v>
+        <v>267</v>
       </c>
       <c r="H437" t="s">
-        <v>167</v>
+        <v>273</v>
       </c>
       <c r="K437">
         <v>143.31</v>
@@ -11162,13 +11480,13 @@
     </row>
     <row r="438" spans="6:15">
       <c r="F438" t="s">
-        <v>32</v>
+        <v>218</v>
       </c>
       <c r="G438" t="s">
-        <v>160</v>
+        <v>266</v>
       </c>
       <c r="H438" t="s">
-        <v>192</v>
+        <v>298</v>
       </c>
       <c r="K438">
         <v>221.66</v>
@@ -11188,10 +11506,10 @@
         <v>21</v>
       </c>
       <c r="G439" t="s">
-        <v>160</v>
+        <v>266</v>
       </c>
       <c r="H439" t="s">
-        <v>192</v>
+        <v>298</v>
       </c>
       <c r="K439">
         <v>221.65</v>
@@ -11208,13 +11526,13 @@
     </row>
     <row r="440" spans="6:15">
       <c r="F440" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G440" t="s">
-        <v>193</v>
+        <v>299</v>
       </c>
       <c r="H440" t="s">
-        <v>161</v>
+        <v>267</v>
       </c>
       <c r="K440">
         <v>1038.66</v>
@@ -11234,10 +11552,10 @@
         <v>21</v>
       </c>
       <c r="G441" t="s">
-        <v>193</v>
+        <v>299</v>
       </c>
       <c r="H441" t="s">
-        <v>161</v>
+        <v>267</v>
       </c>
       <c r="K441">
         <v>2794.65</v>
@@ -11257,10 +11575,10 @@
         <v>21</v>
       </c>
       <c r="G442" t="s">
-        <v>193</v>
+        <v>299</v>
       </c>
       <c r="H442" t="s">
-        <v>161</v>
+        <v>267</v>
       </c>
       <c r="K442">
         <v>1557.33</v>
@@ -11280,10 +11598,10 @@
         <v>21</v>
       </c>
       <c r="G443" t="s">
-        <v>193</v>
+        <v>299</v>
       </c>
       <c r="H443" t="s">
-        <v>161</v>
+        <v>267</v>
       </c>
       <c r="K443">
         <v>1637.33</v>
@@ -11303,10 +11621,10 @@
         <v>21</v>
       </c>
       <c r="G444" t="s">
-        <v>193</v>
+        <v>299</v>
       </c>
       <c r="H444" t="s">
-        <v>161</v>
+        <v>267</v>
       </c>
       <c r="K444">
         <v>978.66</v>
@@ -11323,13 +11641,13 @@
     </row>
     <row r="445" spans="6:15">
       <c r="F445" t="s">
-        <v>100</v>
+        <v>219</v>
       </c>
       <c r="G445" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="H445" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="K445">
         <v>123.33</v>
@@ -11346,13 +11664,13 @@
     </row>
     <row r="446" spans="6:15">
       <c r="F446" t="s">
-        <v>101</v>
+        <v>149</v>
       </c>
       <c r="G446" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="H446" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="K446">
         <v>104.66</v>
@@ -11369,13 +11687,13 @@
     </row>
     <row r="447" spans="6:15">
       <c r="F447" t="s">
-        <v>101</v>
+        <v>149</v>
       </c>
       <c r="G447" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="H447" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="K447">
         <v>508.66</v>
@@ -11392,13 +11710,13 @@
     </row>
     <row r="448" spans="6:15">
       <c r="F448" t="s">
-        <v>15</v>
+        <v>220</v>
       </c>
       <c r="G448" t="s">
-        <v>144</v>
+        <v>250</v>
       </c>
       <c r="H448" t="s">
-        <v>184</v>
+        <v>290</v>
       </c>
       <c r="K448">
         <v>138.66</v>
@@ -11415,13 +11733,13 @@
     </row>
     <row r="449" spans="6:15">
       <c r="F449" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G449" t="s">
-        <v>205</v>
+        <v>311</v>
       </c>
       <c r="H449" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="K449">
         <v>66.67</v>
@@ -11441,10 +11759,10 @@
         <v>21</v>
       </c>
       <c r="G450" t="s">
-        <v>205</v>
+        <v>311</v>
       </c>
       <c r="H450" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="K450">
         <v>66.66</v>
@@ -11464,10 +11782,10 @@
         <v>16</v>
       </c>
       <c r="G451" t="s">
-        <v>152</v>
+        <v>258</v>
       </c>
       <c r="H451" t="s">
-        <v>187</v>
+        <v>293</v>
       </c>
       <c r="K451">
         <v>15.33</v>
@@ -11487,10 +11805,10 @@
         <v>17</v>
       </c>
       <c r="G452" t="s">
-        <v>152</v>
+        <v>258</v>
       </c>
       <c r="H452" t="s">
-        <v>187</v>
+        <v>293</v>
       </c>
       <c r="K452">
         <v>73.33</v>
@@ -11510,10 +11828,10 @@
         <v>17</v>
       </c>
       <c r="G453" t="s">
-        <v>185</v>
+        <v>291</v>
       </c>
       <c r="H453" t="s">
-        <v>187</v>
+        <v>293</v>
       </c>
       <c r="K453">
         <v>76.66</v>
@@ -11530,13 +11848,13 @@
     </row>
     <row r="454" spans="6:15">
       <c r="F454" t="s">
-        <v>83</v>
+        <v>221</v>
       </c>
       <c r="G454" t="s">
-        <v>205</v>
+        <v>311</v>
       </c>
       <c r="H454" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="K454">
         <v>148.66</v>
@@ -11553,13 +11871,13 @@
     </row>
     <row r="455" spans="6:15">
       <c r="F455" t="s">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="G455" t="s">
-        <v>205</v>
+        <v>311</v>
       </c>
       <c r="H455" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="K455">
         <v>192.99</v>
@@ -11576,13 +11894,13 @@
     </row>
     <row r="456" spans="6:15">
       <c r="F456" t="s">
-        <v>22</v>
+        <v>222</v>
       </c>
       <c r="G456" t="s">
-        <v>160</v>
+        <v>266</v>
       </c>
       <c r="H456" t="s">
-        <v>192</v>
+        <v>298</v>
       </c>
       <c r="K456">
         <v>346.63</v>
@@ -11599,13 +11917,13 @@
     </row>
     <row r="457" spans="6:15">
       <c r="F457" t="s">
-        <v>133</v>
+        <v>223</v>
       </c>
       <c r="G457" t="s">
-        <v>161</v>
+        <v>267</v>
       </c>
       <c r="H457" t="s">
-        <v>161</v>
+        <v>267</v>
       </c>
       <c r="K457">
         <v>256.66</v>
@@ -11622,13 +11940,13 @@
     </row>
     <row r="458" spans="6:15">
       <c r="F458" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="G458" t="s">
-        <v>161</v>
+        <v>267</v>
       </c>
       <c r="H458" t="s">
-        <v>161</v>
+        <v>267</v>
       </c>
       <c r="K458">
         <v>153.99</v>
@@ -11645,13 +11963,13 @@
     </row>
     <row r="459" spans="6:15">
       <c r="F459" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="G459" t="s">
-        <v>160</v>
+        <v>266</v>
       </c>
       <c r="H459" t="s">
-        <v>192</v>
+        <v>298</v>
       </c>
       <c r="K459">
         <v>126.63</v>
@@ -11668,13 +11986,13 @@
     </row>
     <row r="460" spans="6:15">
       <c r="F460" t="s">
-        <v>20</v>
+        <v>224</v>
       </c>
       <c r="G460" t="s">
-        <v>192</v>
+        <v>298</v>
       </c>
       <c r="H460" t="s">
-        <v>192</v>
+        <v>298</v>
       </c>
       <c r="K460">
         <v>4986.63</v>
@@ -11694,10 +12012,10 @@
         <v>21</v>
       </c>
       <c r="G461" t="s">
-        <v>192</v>
+        <v>298</v>
       </c>
       <c r="H461" t="s">
-        <v>193</v>
+        <v>299</v>
       </c>
       <c r="K461">
         <v>2169.94</v>
@@ -11717,10 +12035,10 @@
         <v>21</v>
       </c>
       <c r="G462" t="s">
-        <v>161</v>
+        <v>267</v>
       </c>
       <c r="H462" t="s">
-        <v>167</v>
+        <v>273</v>
       </c>
       <c r="K462">
         <v>1246.66</v>
@@ -11740,10 +12058,10 @@
         <v>21</v>
       </c>
       <c r="G463" t="s">
-        <v>161</v>
+        <v>267</v>
       </c>
       <c r="H463" t="s">
-        <v>167</v>
+        <v>273</v>
       </c>
       <c r="K463">
         <v>996.66</v>
@@ -11760,13 +12078,13 @@
     </row>
     <row r="464" spans="6:15">
       <c r="F464" t="s">
-        <v>65</v>
+        <v>225</v>
       </c>
       <c r="G464" t="s">
-        <v>201</v>
+        <v>307</v>
       </c>
       <c r="H464" t="s">
-        <v>186</v>
+        <v>292</v>
       </c>
       <c r="K464">
         <v>124.33</v>
@@ -11783,13 +12101,13 @@
     </row>
     <row r="465" spans="6:15">
       <c r="F465" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="G465" t="s">
-        <v>201</v>
+        <v>307</v>
       </c>
       <c r="H465" t="s">
-        <v>186</v>
+        <v>292</v>
       </c>
       <c r="K465">
         <v>124.33</v>
@@ -11806,13 +12124,13 @@
     </row>
     <row r="466" spans="6:15">
       <c r="F466" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="G466" t="s">
-        <v>201</v>
+        <v>307</v>
       </c>
       <c r="H466" t="s">
-        <v>186</v>
+        <v>292</v>
       </c>
       <c r="K466">
         <v>252.66</v>
@@ -11829,13 +12147,13 @@
     </row>
     <row r="467" spans="6:15">
       <c r="F467" t="s">
-        <v>65</v>
+        <v>226</v>
       </c>
       <c r="G467" t="s">
-        <v>187</v>
+        <v>293</v>
       </c>
       <c r="H467" t="s">
-        <v>225</v>
+        <v>331</v>
       </c>
       <c r="K467">
         <v>118.66</v>
@@ -11852,13 +12170,13 @@
     </row>
     <row r="468" spans="6:15">
       <c r="F468" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="G468" t="s">
-        <v>187</v>
+        <v>293</v>
       </c>
       <c r="H468" t="s">
-        <v>225</v>
+        <v>331</v>
       </c>
       <c r="K468">
         <v>153.99</v>
@@ -11875,13 +12193,13 @@
     </row>
     <row r="469" spans="6:15">
       <c r="F469" t="s">
-        <v>44</v>
+        <v>227</v>
       </c>
       <c r="G469" t="s">
-        <v>208</v>
+        <v>314</v>
       </c>
       <c r="H469" t="s">
-        <v>210</v>
+        <v>316</v>
       </c>
       <c r="K469">
         <v>298.01</v>
@@ -11898,13 +12216,13 @@
     </row>
     <row r="470" spans="6:15">
       <c r="F470" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G470" t="s">
-        <v>208</v>
+        <v>314</v>
       </c>
       <c r="H470" t="s">
-        <v>210</v>
+        <v>316</v>
       </c>
       <c r="K470">
         <v>198.67</v>
@@ -11921,13 +12239,13 @@
     </row>
     <row r="471" spans="6:15">
       <c r="F471" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G471" t="s">
-        <v>208</v>
+        <v>314</v>
       </c>
       <c r="H471" t="s">
-        <v>210</v>
+        <v>316</v>
       </c>
       <c r="K471">
         <v>661.6799999999999</v>
@@ -11944,13 +12262,13 @@
     </row>
     <row r="472" spans="6:15">
       <c r="F472" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G472" t="s">
-        <v>208</v>
+        <v>314</v>
       </c>
       <c r="H472" t="s">
-        <v>230</v>
+        <v>336</v>
       </c>
       <c r="K472">
         <v>583.36</v>
@@ -11967,13 +12285,13 @@
     </row>
     <row r="473" spans="6:15">
       <c r="F473" t="s">
-        <v>134</v>
+        <v>228</v>
       </c>
       <c r="G473" t="s">
-        <v>210</v>
+        <v>316</v>
       </c>
       <c r="H473" t="s">
-        <v>230</v>
+        <v>336</v>
       </c>
       <c r="K473">
         <v>1717.36</v>
@@ -11990,13 +12308,13 @@
     </row>
     <row r="474" spans="6:15">
       <c r="F474" t="s">
-        <v>135</v>
+        <v>229</v>
       </c>
       <c r="G474" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="H474" t="s">
-        <v>176</v>
+        <v>282</v>
       </c>
       <c r="K474">
         <v>474.65</v>
@@ -12013,13 +12331,13 @@
     </row>
     <row r="475" spans="6:15">
       <c r="F475" t="s">
-        <v>136</v>
+        <v>230</v>
       </c>
       <c r="G475" t="s">
-        <v>213</v>
+        <v>319</v>
       </c>
       <c r="H475" t="s">
-        <v>214</v>
+        <v>320</v>
       </c>
       <c r="K475">
         <v>153.36</v>
@@ -12036,13 +12354,13 @@
     </row>
     <row r="476" spans="6:15">
       <c r="F476" t="s">
-        <v>106</v>
+        <v>231</v>
       </c>
       <c r="G476" t="s">
-        <v>214</v>
+        <v>320</v>
       </c>
       <c r="H476" t="s">
-        <v>147</v>
+        <v>253</v>
       </c>
       <c r="K476">
         <v>271.68</v>
@@ -12059,13 +12377,13 @@
     </row>
     <row r="477" spans="6:15">
       <c r="F477" t="s">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="G477" t="s">
-        <v>214</v>
+        <v>320</v>
       </c>
       <c r="H477" t="s">
-        <v>147</v>
+        <v>253</v>
       </c>
       <c r="K477">
         <v>271.68</v>
@@ -12082,13 +12400,13 @@
     </row>
     <row r="478" spans="6:15">
       <c r="F478" t="s">
-        <v>23</v>
+        <v>152</v>
       </c>
       <c r="G478" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="H478" t="s">
-        <v>209</v>
+        <v>315</v>
       </c>
       <c r="K478">
         <v>1286.72</v>
@@ -12105,13 +12423,13 @@
     </row>
     <row r="479" spans="6:15">
       <c r="F479" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G479" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="H479" t="s">
-        <v>209</v>
+        <v>315</v>
       </c>
       <c r="K479">
         <v>772.03</v>
@@ -12128,13 +12446,13 @@
     </row>
     <row r="480" spans="6:15">
       <c r="F480" t="s">
-        <v>110</v>
+        <v>232</v>
       </c>
       <c r="G480" t="s">
-        <v>227</v>
+        <v>333</v>
       </c>
       <c r="H480" t="s">
-        <v>236</v>
+        <v>342</v>
       </c>
       <c r="K480">
         <v>0</v>
@@ -12151,13 +12469,13 @@
     </row>
     <row r="481" spans="6:15">
       <c r="F481" t="s">
-        <v>80</v>
+        <v>181</v>
       </c>
       <c r="G481" t="s">
-        <v>147</v>
+        <v>253</v>
       </c>
       <c r="H481" t="s">
-        <v>232</v>
+        <v>338</v>
       </c>
       <c r="K481">
         <v>178.34</v>
@@ -12174,13 +12492,13 @@
     </row>
     <row r="482" spans="6:15">
       <c r="F482" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G482" t="s">
-        <v>147</v>
+        <v>253</v>
       </c>
       <c r="H482" t="s">
-        <v>229</v>
+        <v>335</v>
       </c>
       <c r="K482">
         <v>0</v>
@@ -12197,13 +12515,13 @@
     </row>
     <row r="483" spans="6:15">
       <c r="F483" t="s">
-        <v>23</v>
+        <v>233</v>
       </c>
       <c r="G483" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="H483" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="K483">
         <v>2393.31</v>
@@ -12220,13 +12538,13 @@
     </row>
     <row r="484" spans="6:15">
       <c r="F484" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G484" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="H484" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="K484">
         <v>571.66</v>
@@ -12243,13 +12561,13 @@
     </row>
     <row r="485" spans="6:15">
       <c r="F485" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G485" t="s">
-        <v>212</v>
+        <v>318</v>
       </c>
       <c r="H485" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="K485">
         <v>796.66</v>
@@ -12266,13 +12584,13 @@
     </row>
     <row r="486" spans="6:15">
       <c r="F486" t="s">
-        <v>23</v>
+        <v>189</v>
       </c>
       <c r="G486" t="s">
-        <v>228</v>
+        <v>334</v>
       </c>
       <c r="H486" t="s">
-        <v>148</v>
+        <v>254</v>
       </c>
       <c r="K486">
         <v>796.6799999999999</v>
@@ -12289,13 +12607,13 @@
     </row>
     <row r="487" spans="6:15">
       <c r="F487" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G487" t="s">
-        <v>228</v>
+        <v>334</v>
       </c>
       <c r="H487" t="s">
-        <v>148</v>
+        <v>254</v>
       </c>
       <c r="K487">
         <v>166.33</v>
@@ -12312,13 +12630,13 @@
     </row>
     <row r="488" spans="6:15">
       <c r="F488" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G488" t="s">
-        <v>228</v>
+        <v>334</v>
       </c>
       <c r="H488" t="s">
-        <v>148</v>
+        <v>254</v>
       </c>
       <c r="K488">
         <v>166.34</v>
@@ -12335,13 +12653,13 @@
     </row>
     <row r="489" spans="6:15">
       <c r="F489" t="s">
-        <v>127</v>
+        <v>234</v>
       </c>
       <c r="G489" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="H489" t="s">
-        <v>176</v>
+        <v>282</v>
       </c>
       <c r="K489">
         <v>893.3099999999999</v>
@@ -12358,13 +12676,13 @@
     </row>
     <row r="490" spans="6:15">
       <c r="F490" t="s">
-        <v>90</v>
+        <v>137</v>
       </c>
       <c r="G490" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="H490" t="s">
-        <v>176</v>
+        <v>282</v>
       </c>
       <c r="K490">
         <v>1043.31</v>
@@ -12381,13 +12699,13 @@
     </row>
     <row r="491" spans="6:15">
       <c r="F491" t="s">
-        <v>138</v>
+        <v>235</v>
       </c>
       <c r="G491" t="s">
-        <v>192</v>
+        <v>298</v>
       </c>
       <c r="H491" t="s">
-        <v>193</v>
+        <v>299</v>
       </c>
       <c r="K491">
         <v>1323.31</v>
@@ -12404,13 +12722,13 @@
     </row>
     <row r="492" spans="6:15">
       <c r="F492" t="s">
-        <v>139</v>
+        <v>70</v>
       </c>
       <c r="G492" t="s">
-        <v>192</v>
+        <v>298</v>
       </c>
       <c r="H492" t="s">
-        <v>193</v>
+        <v>299</v>
       </c>
       <c r="K492">
         <v>1133.31</v>
@@ -12427,13 +12745,13 @@
     </row>
     <row r="493" spans="6:15">
       <c r="F493" t="s">
-        <v>138</v>
+        <v>236</v>
       </c>
       <c r="G493" t="s">
-        <v>161</v>
+        <v>267</v>
       </c>
       <c r="H493" t="s">
-        <v>167</v>
+        <v>273</v>
       </c>
       <c r="K493">
         <v>1021.66</v>
@@ -12450,13 +12768,13 @@
     </row>
     <row r="494" spans="6:15">
       <c r="F494" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="G494" t="s">
-        <v>161</v>
+        <v>267</v>
       </c>
       <c r="H494" t="s">
-        <v>167</v>
+        <v>273</v>
       </c>
       <c r="K494">
         <v>1009.66</v>
@@ -12473,13 +12791,13 @@
     </row>
     <row r="495" spans="6:15">
       <c r="F495" t="s">
-        <v>97</v>
+        <v>237</v>
       </c>
       <c r="G495" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="H495" t="s">
-        <v>176</v>
+        <v>282</v>
       </c>
       <c r="K495">
         <v>317.33</v>
@@ -12496,13 +12814,13 @@
     </row>
     <row r="496" spans="6:15">
       <c r="F496" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G496" t="s">
-        <v>161</v>
+        <v>267</v>
       </c>
       <c r="H496" t="s">
-        <v>167</v>
+        <v>273</v>
       </c>
       <c r="K496">
         <v>463.31</v>
@@ -12519,13 +12837,13 @@
     </row>
     <row r="497" spans="6:15">
       <c r="F497" t="s">
-        <v>77</v>
+        <v>238</v>
       </c>
       <c r="G497" t="s">
-        <v>161</v>
+        <v>267</v>
       </c>
       <c r="H497" t="s">
-        <v>167</v>
+        <v>273</v>
       </c>
       <c r="K497">
         <v>174.99</v>
@@ -12542,13 +12860,13 @@
     </row>
     <row r="498" spans="6:15">
       <c r="F498" t="s">
-        <v>44</v>
+        <v>239</v>
       </c>
       <c r="G498" t="s">
-        <v>208</v>
+        <v>314</v>
       </c>
       <c r="H498" t="s">
-        <v>210</v>
+        <v>316</v>
       </c>
       <c r="K498">
         <v>1086.68</v>
@@ -12565,13 +12883,13 @@
     </row>
     <row r="499" spans="6:15">
       <c r="F499" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G499" t="s">
-        <v>208</v>
+        <v>314</v>
       </c>
       <c r="H499" t="s">
-        <v>210</v>
+        <v>316</v>
       </c>
       <c r="K499">
         <v>1041.68</v>
@@ -12588,13 +12906,13 @@
     </row>
     <row r="500" spans="6:15">
       <c r="F500" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G500" t="s">
-        <v>208</v>
+        <v>314</v>
       </c>
       <c r="H500" t="s">
-        <v>230</v>
+        <v>336</v>
       </c>
       <c r="K500">
         <v>693.36</v>
@@ -12611,13 +12929,13 @@
     </row>
     <row r="501" spans="6:15">
       <c r="F501" t="s">
-        <v>56</v>
+        <v>240</v>
       </c>
       <c r="G501" t="s">
-        <v>213</v>
+        <v>319</v>
       </c>
       <c r="H501" t="s">
-        <v>214</v>
+        <v>320</v>
       </c>
       <c r="K501">
         <v>158.67</v>
@@ -12634,13 +12952,13 @@
     </row>
     <row r="502" spans="6:15">
       <c r="F502" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="G502" t="s">
-        <v>213</v>
+        <v>319</v>
       </c>
       <c r="H502" t="s">
-        <v>214</v>
+        <v>320</v>
       </c>
       <c r="K502">
         <v>238.01</v>
@@ -12657,13 +12975,13 @@
     </row>
     <row r="503" spans="6:15">
       <c r="F503" t="s">
-        <v>134</v>
+        <v>241</v>
       </c>
       <c r="G503" t="s">
-        <v>158</v>
+        <v>264</v>
       </c>
       <c r="H503" t="s">
-        <v>234</v>
+        <v>340</v>
       </c>
       <c r="K503">
         <v>377.69</v>
@@ -12680,13 +12998,13 @@
     </row>
     <row r="504" spans="6:15">
       <c r="F504" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="G504" t="s">
-        <v>229</v>
+        <v>335</v>
       </c>
       <c r="H504" t="s">
-        <v>146</v>
+        <v>252</v>
       </c>
       <c r="K504">
         <v>993.36</v>
@@ -12703,13 +13021,13 @@
     </row>
     <row r="505" spans="6:15">
       <c r="F505" t="s">
-        <v>44</v>
+        <v>242</v>
       </c>
       <c r="G505" t="s">
-        <v>148</v>
+        <v>254</v>
       </c>
       <c r="H505" t="s">
-        <v>229</v>
+        <v>335</v>
       </c>
       <c r="K505">
         <v>200.34</v>
@@ -12726,13 +13044,13 @@
     </row>
     <row r="506" spans="6:15">
       <c r="F506" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="G506" t="s">
-        <v>148</v>
+        <v>254</v>
       </c>
       <c r="H506" t="s">
-        <v>229</v>
+        <v>335</v>
       </c>
       <c r="K506">
         <v>991.6799999999999</v>
@@ -12749,13 +13067,13 @@
     </row>
     <row r="507" spans="6:15">
       <c r="F507" t="s">
-        <v>140</v>
+        <v>243</v>
       </c>
       <c r="G507" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="H507" t="s">
-        <v>176</v>
+        <v>282</v>
       </c>
       <c r="K507">
         <v>241.33</v>
@@ -12772,13 +13090,13 @@
     </row>
     <row r="508" spans="6:15">
       <c r="F508" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G508" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="H508" t="s">
-        <v>176</v>
+        <v>282</v>
       </c>
       <c r="K508">
         <v>697.33</v>
@@ -12795,13 +13113,13 @@
     </row>
     <row r="509" spans="6:15">
       <c r="F509" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="G509" t="s">
-        <v>159</v>
+        <v>265</v>
       </c>
       <c r="H509" t="s">
-        <v>192</v>
+        <v>298</v>
       </c>
       <c r="K509">
         <v>0</v>
@@ -12818,13 +13136,13 @@
     </row>
     <row r="510" spans="6:15">
       <c r="F510" t="s">
-        <v>104</v>
+        <v>244</v>
       </c>
       <c r="G510" t="s">
-        <v>157</v>
+        <v>263</v>
       </c>
       <c r="H510" t="s">
-        <v>154</v>
+        <v>260</v>
       </c>
       <c r="K510">
         <v>577.3</v>
@@ -12841,13 +13159,13 @@
     </row>
     <row r="511" spans="6:15">
       <c r="F511" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="G511" t="s">
-        <v>157</v>
+        <v>263</v>
       </c>
       <c r="H511" t="s">
-        <v>154</v>
+        <v>260</v>
       </c>
       <c r="K511">
         <v>438.65</v>
@@ -12864,13 +13182,13 @@
     </row>
     <row r="512" spans="6:15">
       <c r="F512" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="G512" t="s">
-        <v>157</v>
+        <v>263</v>
       </c>
       <c r="H512" t="s">
-        <v>154</v>
+        <v>260</v>
       </c>
       <c r="K512">
         <v>897.3</v>
@@ -12887,13 +13205,13 @@
     </row>
     <row r="513" spans="6:15">
       <c r="F513" t="s">
-        <v>141</v>
+        <v>245</v>
       </c>
       <c r="G513" t="s">
-        <v>230</v>
+        <v>336</v>
       </c>
       <c r="H513" t="s">
-        <v>158</v>
+        <v>264</v>
       </c>
       <c r="K513">
         <v>4266.72</v>
@@ -12910,13 +13228,13 @@
     </row>
     <row r="514" spans="6:15">
       <c r="F514" t="s">
-        <v>142</v>
+        <v>246</v>
       </c>
       <c r="G514" t="s">
-        <v>216</v>
+        <v>322</v>
       </c>
       <c r="H514" t="s">
-        <v>208</v>
+        <v>314</v>
       </c>
       <c r="K514">
         <v>3023.36</v>
@@ -12933,13 +13251,13 @@
     </row>
     <row r="515" spans="6:15">
       <c r="F515" t="s">
-        <v>42</v>
+        <v>247</v>
       </c>
       <c r="G515" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="H515" t="s">
-        <v>159</v>
+        <v>265</v>
       </c>
       <c r="K515">
         <v>41.66</v>
@@ -12956,13 +13274,13 @@
     </row>
     <row r="516" spans="6:15">
       <c r="F516" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="G516" t="s">
-        <v>176</v>
+        <v>282</v>
       </c>
       <c r="H516" t="s">
-        <v>159</v>
+        <v>265</v>
       </c>
       <c r="K516">
         <v>41.65</v>
@@ -12979,13 +13297,13 @@
     </row>
     <row r="517" spans="6:15">
       <c r="F517" t="s">
-        <v>42</v>
+        <v>248</v>
       </c>
       <c r="G517" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="H517" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="K517">
         <v>308.33</v>
@@ -13002,13 +13320,13 @@
     </row>
     <row r="518" spans="6:15">
       <c r="F518" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="G518" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="H518" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="K518">
         <v>782.66</v>
@@ -13025,13 +13343,13 @@
     </row>
     <row r="519" spans="6:15">
       <c r="F519" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="G519" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="H519" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="K519">
         <v>912.66</v>
